--- a/data/seat/01-enero2026.xlsx
+++ b/data/seat/01-enero2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Filezilla/2021/Energia/2026/Enero/31-01-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{420E2FE5-4BF0-45A0-82CB-E4E7EB31347A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD0D524-0BAD-45B2-AFE0-08A8C173D8CA}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{420E2FE5-4BF0-45A0-82CB-E4E7EB31347A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D1F59BA-B53C-49D2-8B81-23DCA35D3028}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,7 +362,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>Fecha</t>
   </si>
@@ -579,27 +579,19 @@
   <si>
     <t>17.45</t>
   </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>D/F</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;Kwh&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;Kw&quot;"/>
     <numFmt numFmtId="167" formatCode="h:mm\ &quot;hrs&quot;\ "/>
     <numFmt numFmtId="168" formatCode="[h]:mm"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;Kwh&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1622,7 +1614,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="326">
+  <cellXfs count="330">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2078,183 +2070,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="63" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2474,6 +2289,193 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="10" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -3683,40 +3685,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>23868.91</c:v>
+                  <c:v>23371.91</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44488</c:v>
+                  <c:v>43991</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26599</c:v>
+                  <c:v>26102</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21155</c:v>
+                  <c:v>20658</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45044</c:v>
+                  <c:v>44547</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47772</c:v>
+                  <c:v>47275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>47375</c:v>
+                  <c:v>46878</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47820</c:v>
+                  <c:v>47323</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>48235</c:v>
+                  <c:v>47738</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>27706</c:v>
+                  <c:v>27209</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21790</c:v>
+                  <c:v>21293</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>45738.01</c:v>
+                  <c:v>45241.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3970,43 +3972,43 @@
             <c:numRef>
               <c:f>'SEAT-SERs'!$H$7:$H$18</c:f>
               <c:numCache>
-                <c:formatCode>#,##0\ "Kwh"</c:formatCode>
+                <c:formatCode>#,##0.00\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>6355.09</c:v>
+                  <c:v>6852.09</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6442</c:v>
+                  <c:v>6939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6247</c:v>
+                  <c:v>6744</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6661</c:v>
+                  <c:v>7158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6572</c:v>
+                  <c:v>7069</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6730</c:v>
+                  <c:v>7227</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6793</c:v>
+                  <c:v>7290</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6758</c:v>
+                  <c:v>7255</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6733</c:v>
+                  <c:v>7230</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6382</c:v>
+                  <c:v>6879</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6294</c:v>
+                  <c:v>6791</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6661.99</c:v>
+                  <c:v>7158.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4101,7 +4103,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\ &quot;Kwh&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0.00\ &quot;Kwh&quot;" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7204,7 +7206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS42"/>
+  <dimension ref="A1:BU42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="133" customWidth="1"/>
@@ -7257,301 +7259,301 @@
     <col min="70" max="70" width="9.28515625" style="14" customWidth="1"/>
     <col min="71" max="71" width="2.7109375" style="14" customWidth="1"/>
     <col min="72" max="72" width="6.85546875" style="14" customWidth="1"/>
-    <col min="73" max="73" width="6.42578125" style="14" customWidth="1"/>
+    <col min="73" max="73" width="11.28515625" style="14" customWidth="1"/>
     <col min="74" max="16384" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="132" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" s="132" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="126">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="271" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="127"/>
-      <c r="D1" s="205" t="s">
+      <c r="D1" s="273" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="207"/>
-      <c r="P1" s="208"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="274"/>
+      <c r="I1" s="274"/>
+      <c r="J1" s="274"/>
+      <c r="K1" s="274"/>
+      <c r="L1" s="274"/>
+      <c r="M1" s="274"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="275"/>
+      <c r="P1" s="276"/>
       <c r="Q1" s="128"/>
-      <c r="R1" s="185" t="s">
+      <c r="R1" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="186"/>
-      <c r="T1" s="186"/>
-      <c r="U1" s="186"/>
-      <c r="V1" s="186"/>
-      <c r="W1" s="186"/>
-      <c r="X1" s="186"/>
-      <c r="Y1" s="186"/>
-      <c r="Z1" s="186"/>
-      <c r="AA1" s="187"/>
+      <c r="S1" s="282"/>
+      <c r="T1" s="282"/>
+      <c r="U1" s="282"/>
+      <c r="V1" s="282"/>
+      <c r="W1" s="282"/>
+      <c r="X1" s="282"/>
+      <c r="Y1" s="282"/>
+      <c r="Z1" s="282"/>
+      <c r="AA1" s="283"/>
       <c r="AB1" s="129"/>
-      <c r="AC1" s="185" t="s">
+      <c r="AC1" s="281" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="186"/>
-      <c r="AE1" s="186"/>
-      <c r="AF1" s="186"/>
-      <c r="AG1" s="186"/>
-      <c r="AH1" s="186"/>
-      <c r="AI1" s="186"/>
-      <c r="AJ1" s="186"/>
-      <c r="AK1" s="187"/>
+      <c r="AD1" s="282"/>
+      <c r="AE1" s="282"/>
+      <c r="AF1" s="282"/>
+      <c r="AG1" s="282"/>
+      <c r="AH1" s="282"/>
+      <c r="AI1" s="282"/>
+      <c r="AJ1" s="282"/>
+      <c r="AK1" s="283"/>
       <c r="AL1" s="130"/>
-      <c r="AM1" s="185" t="s">
+      <c r="AM1" s="281" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="186"/>
-      <c r="AO1" s="186"/>
-      <c r="AP1" s="186"/>
-      <c r="AQ1" s="186"/>
-      <c r="AR1" s="186"/>
-      <c r="AS1" s="186"/>
-      <c r="AT1" s="186"/>
-      <c r="AU1" s="187"/>
+      <c r="AN1" s="282"/>
+      <c r="AO1" s="282"/>
+      <c r="AP1" s="282"/>
+      <c r="AQ1" s="282"/>
+      <c r="AR1" s="282"/>
+      <c r="AS1" s="282"/>
+      <c r="AT1" s="282"/>
+      <c r="AU1" s="283"/>
       <c r="AV1" s="130"/>
-      <c r="AW1" s="185" t="s">
+      <c r="AW1" s="281" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="186"/>
-      <c r="AY1" s="186"/>
-      <c r="AZ1" s="186"/>
-      <c r="BA1" s="186"/>
-      <c r="BB1" s="186"/>
-      <c r="BC1" s="186"/>
-      <c r="BD1" s="186"/>
-      <c r="BE1" s="186"/>
-      <c r="BF1" s="186"/>
-      <c r="BG1" s="186"/>
-      <c r="BH1" s="187"/>
+      <c r="AX1" s="282"/>
+      <c r="AY1" s="282"/>
+      <c r="AZ1" s="282"/>
+      <c r="BA1" s="282"/>
+      <c r="BB1" s="282"/>
+      <c r="BC1" s="282"/>
+      <c r="BD1" s="282"/>
+      <c r="BE1" s="282"/>
+      <c r="BF1" s="282"/>
+      <c r="BG1" s="282"/>
+      <c r="BH1" s="283"/>
       <c r="BI1" s="130"/>
-      <c r="BJ1" s="185" t="s">
+      <c r="BJ1" s="281" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="186"/>
-      <c r="BL1" s="186"/>
-      <c r="BM1" s="186"/>
-      <c r="BN1" s="186"/>
-      <c r="BO1" s="186"/>
-      <c r="BP1" s="186"/>
-      <c r="BQ1" s="186"/>
-      <c r="BR1" s="187"/>
+      <c r="BK1" s="282"/>
+      <c r="BL1" s="282"/>
+      <c r="BM1" s="282"/>
+      <c r="BN1" s="282"/>
+      <c r="BO1" s="282"/>
+      <c r="BP1" s="282"/>
+      <c r="BQ1" s="282"/>
+      <c r="BR1" s="283"/>
       <c r="BS1" s="131"/>
     </row>
-    <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="203"/>
+    <row r="2" spans="1:73" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="271"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="212"/>
+      <c r="D2" s="277"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="278"/>
+      <c r="K2" s="278"/>
+      <c r="L2" s="278"/>
+      <c r="M2" s="278"/>
+      <c r="N2" s="278"/>
+      <c r="O2" s="279"/>
+      <c r="P2" s="280"/>
       <c r="Q2" s="58"/>
-      <c r="R2" s="188"/>
-      <c r="S2" s="189"/>
-      <c r="T2" s="189"/>
-      <c r="U2" s="189"/>
-      <c r="V2" s="189"/>
-      <c r="W2" s="189"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="190"/>
+      <c r="R2" s="284"/>
+      <c r="S2" s="285"/>
+      <c r="T2" s="285"/>
+      <c r="U2" s="285"/>
+      <c r="V2" s="285"/>
+      <c r="W2" s="285"/>
+      <c r="X2" s="285"/>
+      <c r="Y2" s="285"/>
+      <c r="Z2" s="285"/>
+      <c r="AA2" s="286"/>
       <c r="AB2" s="60"/>
-      <c r="AC2" s="188"/>
-      <c r="AD2" s="189"/>
-      <c r="AE2" s="189"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="189"/>
-      <c r="AH2" s="189"/>
-      <c r="AI2" s="189"/>
-      <c r="AJ2" s="189"/>
-      <c r="AK2" s="190"/>
+      <c r="AC2" s="284"/>
+      <c r="AD2" s="285"/>
+      <c r="AE2" s="285"/>
+      <c r="AF2" s="285"/>
+      <c r="AG2" s="285"/>
+      <c r="AH2" s="285"/>
+      <c r="AI2" s="285"/>
+      <c r="AJ2" s="285"/>
+      <c r="AK2" s="286"/>
       <c r="AL2" s="59"/>
-      <c r="AM2" s="188"/>
-      <c r="AN2" s="189"/>
-      <c r="AO2" s="189"/>
-      <c r="AP2" s="189"/>
-      <c r="AQ2" s="189"/>
-      <c r="AR2" s="189"/>
-      <c r="AS2" s="189"/>
-      <c r="AT2" s="189"/>
-      <c r="AU2" s="190"/>
+      <c r="AM2" s="284"/>
+      <c r="AN2" s="285"/>
+      <c r="AO2" s="285"/>
+      <c r="AP2" s="285"/>
+      <c r="AQ2" s="285"/>
+      <c r="AR2" s="285"/>
+      <c r="AS2" s="285"/>
+      <c r="AT2" s="285"/>
+      <c r="AU2" s="286"/>
       <c r="AV2" s="59"/>
-      <c r="AW2" s="188"/>
-      <c r="AX2" s="189"/>
-      <c r="AY2" s="189"/>
-      <c r="AZ2" s="189"/>
-      <c r="BA2" s="189"/>
-      <c r="BB2" s="189"/>
-      <c r="BC2" s="189"/>
-      <c r="BD2" s="189"/>
-      <c r="BE2" s="189"/>
-      <c r="BF2" s="189"/>
-      <c r="BG2" s="189"/>
-      <c r="BH2" s="190"/>
+      <c r="AW2" s="284"/>
+      <c r="AX2" s="285"/>
+      <c r="AY2" s="285"/>
+      <c r="AZ2" s="285"/>
+      <c r="BA2" s="285"/>
+      <c r="BB2" s="285"/>
+      <c r="BC2" s="285"/>
+      <c r="BD2" s="285"/>
+      <c r="BE2" s="285"/>
+      <c r="BF2" s="285"/>
+      <c r="BG2" s="285"/>
+      <c r="BH2" s="286"/>
       <c r="BI2" s="59"/>
-      <c r="BJ2" s="188"/>
-      <c r="BK2" s="189"/>
-      <c r="BL2" s="189"/>
-      <c r="BM2" s="189"/>
-      <c r="BN2" s="189"/>
-      <c r="BO2" s="189"/>
-      <c r="BP2" s="189"/>
-      <c r="BQ2" s="189"/>
-      <c r="BR2" s="190"/>
+      <c r="BJ2" s="284"/>
+      <c r="BK2" s="285"/>
+      <c r="BL2" s="285"/>
+      <c r="BM2" s="285"/>
+      <c r="BN2" s="285"/>
+      <c r="BO2" s="285"/>
+      <c r="BP2" s="285"/>
+      <c r="BQ2" s="285"/>
+      <c r="BR2" s="286"/>
       <c r="BS2" s="134"/>
     </row>
-    <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="203"/>
+    <row r="3" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="271"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="191" t="s">
+      <c r="D3" s="290" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="191" t="s">
+      <c r="E3" s="290" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="191" t="s">
+      <c r="F3" s="290" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="191" t="s">
+      <c r="G3" s="290" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="191" t="s">
+      <c r="H3" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="213" t="s">
+      <c r="I3" s="292" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="214"/>
-      <c r="K3" s="215"/>
-      <c r="L3" s="216"/>
-      <c r="M3" s="213" t="s">
+      <c r="J3" s="293"/>
+      <c r="K3" s="294"/>
+      <c r="L3" s="295"/>
+      <c r="M3" s="292" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="214"/>
-      <c r="O3" s="215"/>
-      <c r="P3" s="216"/>
+      <c r="N3" s="293"/>
+      <c r="O3" s="294"/>
+      <c r="P3" s="295"/>
       <c r="Q3" s="58"/>
-      <c r="R3" s="195" t="s">
+      <c r="R3" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="196"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="195" t="s">
+      <c r="S3" s="288"/>
+      <c r="T3" s="297"/>
+      <c r="U3" s="297"/>
+      <c r="V3" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="196"/>
-      <c r="X3" s="196"/>
-      <c r="Y3" s="196"/>
-      <c r="Z3" s="196"/>
-      <c r="AA3" s="197"/>
+      <c r="W3" s="288"/>
+      <c r="X3" s="288"/>
+      <c r="Y3" s="288"/>
+      <c r="Z3" s="288"/>
+      <c r="AA3" s="289"/>
       <c r="AB3" s="60"/>
-      <c r="AC3" s="193" t="s">
+      <c r="AC3" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="218" t="s">
+      <c r="AD3" s="300" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="195" t="s">
+      <c r="AE3" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="196"/>
-      <c r="AG3" s="197"/>
-      <c r="AH3" s="195" t="s">
+      <c r="AF3" s="288"/>
+      <c r="AG3" s="289"/>
+      <c r="AH3" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="196"/>
-      <c r="AJ3" s="196"/>
-      <c r="AK3" s="197"/>
+      <c r="AI3" s="288"/>
+      <c r="AJ3" s="288"/>
+      <c r="AK3" s="289"/>
       <c r="AL3" s="59"/>
-      <c r="AM3" s="198" t="s">
+      <c r="AM3" s="301" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="193" t="s">
+      <c r="AN3" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="202" t="s">
+      <c r="AO3" s="287" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="196"/>
-      <c r="AQ3" s="197"/>
-      <c r="AR3" s="195" t="s">
+      <c r="AP3" s="288"/>
+      <c r="AQ3" s="289"/>
+      <c r="AR3" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="196"/>
-      <c r="AT3" s="196"/>
-      <c r="AU3" s="197"/>
+      <c r="AS3" s="288"/>
+      <c r="AT3" s="288"/>
+      <c r="AU3" s="289"/>
       <c r="AV3" s="59"/>
-      <c r="AW3" s="193" t="s">
+      <c r="AW3" s="298" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="193" t="s">
+      <c r="AX3" s="298" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="202" t="s">
+      <c r="AY3" s="287" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="202"/>
-      <c r="BA3" s="196"/>
-      <c r="BB3" s="197"/>
-      <c r="BC3" s="195" t="s">
+      <c r="AZ3" s="287"/>
+      <c r="BA3" s="288"/>
+      <c r="BB3" s="289"/>
+      <c r="BC3" s="296" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="202"/>
-      <c r="BE3" s="202"/>
-      <c r="BF3" s="196"/>
-      <c r="BG3" s="196"/>
-      <c r="BH3" s="197"/>
+      <c r="BD3" s="287"/>
+      <c r="BE3" s="287"/>
+      <c r="BF3" s="288"/>
+      <c r="BG3" s="288"/>
+      <c r="BH3" s="289"/>
       <c r="BI3" s="59"/>
-      <c r="BJ3" s="198" t="s">
+      <c r="BJ3" s="301" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="193" t="s">
+      <c r="BK3" s="298" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="199" t="s">
+      <c r="BL3" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="200"/>
-      <c r="BN3" s="201"/>
-      <c r="BO3" s="202" t="s">
+      <c r="BM3" s="303"/>
+      <c r="BN3" s="304"/>
+      <c r="BO3" s="287" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="196"/>
-      <c r="BQ3" s="196"/>
-      <c r="BR3" s="197"/>
+      <c r="BP3" s="288"/>
+      <c r="BQ3" s="288"/>
+      <c r="BR3" s="289"/>
       <c r="BS3" s="134"/>
     </row>
-    <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="204"/>
+    <row r="4" spans="1:73" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="272"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
+      <c r="D4" s="291"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
       <c r="I4" s="80" t="s">
         <v>3</v>
       </c>
@@ -7608,8 +7610,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="60"/>
-      <c r="AC4" s="194"/>
-      <c r="AD4" s="186"/>
+      <c r="AC4" s="299"/>
+      <c r="AD4" s="282"/>
       <c r="AE4" s="62" t="s">
         <v>27</v>
       </c>
@@ -7632,8 +7634,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="61"/>
-      <c r="AM4" s="185"/>
-      <c r="AN4" s="194"/>
+      <c r="AM4" s="281"/>
+      <c r="AN4" s="299"/>
       <c r="AO4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7656,8 +7658,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="61"/>
-      <c r="AW4" s="194"/>
-      <c r="AX4" s="194"/>
+      <c r="AW4" s="299"/>
+      <c r="AX4" s="299"/>
       <c r="AY4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7689,8 +7691,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="61"/>
-      <c r="BJ4" s="185"/>
-      <c r="BK4" s="194"/>
+      <c r="BJ4" s="281"/>
+      <c r="BK4" s="299"/>
       <c r="BL4" s="123" t="s">
         <v>32</v>
       </c>
@@ -7714,7 +7716,7 @@
       </c>
       <c r="BS4" s="135"/>
     </row>
-    <row r="5" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="136"/>
       <c r="C5" s="137"/>
       <c r="D5" s="83"/>
@@ -7786,7 +7788,7 @@
       <c r="BR5" s="66"/>
       <c r="BS5" s="144"/>
     </row>
-    <row r="6" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="167">
         <v>46022</v>
       </c>
@@ -8019,66 +8021,66 @@
         <v>0.66388888888888886</v>
       </c>
     </row>
-    <row r="7" spans="1:71" s="271" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="244"/>
-      <c r="B7" s="245">
+    <row r="7" spans="1:73" s="212" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="185"/>
+      <c r="B7" s="186">
         <f>B6+1</f>
         <v>46023</v>
       </c>
-      <c r="C7" s="246"/>
-      <c r="D7" s="247">
+      <c r="C7" s="187"/>
+      <c r="D7" s="188">
         <f t="shared" ref="D7:D37" si="22">R7</f>
         <v>30224</v>
       </c>
-      <c r="E7" s="248">
+      <c r="E7" s="189">
         <f t="shared" ref="E7:E10" si="23">F7/D7</f>
-        <v>0.78973365537321338</v>
-      </c>
-      <c r="F7" s="247">
+        <v>0.77328976971942831</v>
+      </c>
+      <c r="F7" s="188">
         <f t="shared" ref="F7:F37" si="24">D7-H7</f>
-        <v>23868.91</v>
-      </c>
-      <c r="G7" s="248">
+        <v>23371.91</v>
+      </c>
+      <c r="G7" s="189">
         <f t="shared" ref="G7:G10" si="25">H7/D7</f>
-        <v>0.21026634462678667</v>
-      </c>
-      <c r="H7" s="154">
-        <f t="shared" ref="H7:H37" si="26">U7+AG7+AQ7+BB7</f>
-        <v>6355.09</v>
-      </c>
-      <c r="I7" s="249">
-        <f t="shared" ref="I7:I10" si="27">AE7/(AE7+AO7+BL7+AY7)</f>
+        <v>0.22671023028057175</v>
+      </c>
+      <c r="H7" s="268">
+        <f>U7+AG7+AQ7+BB7</f>
+        <v>6852.09</v>
+      </c>
+      <c r="I7" s="190">
+        <f t="shared" ref="I7:I10" si="26">AE7/(AE7+AO7+BL7+AY7)</f>
         <v>6.144350576707943E-2</v>
       </c>
-      <c r="J7" s="248">
-        <f t="shared" ref="J7:J10" si="28">AO7/(AE7+AO7+BL7+AY7)</f>
+      <c r="J7" s="189">
+        <f t="shared" ref="J7:J10" si="27">AO7/(AE7+AO7+BL7+AY7)</f>
         <v>0.1637001890213324</v>
       </c>
-      <c r="K7" s="248">
-        <f t="shared" ref="K7:K10" si="29">AY7/(AF7+AP7+BM7+AZ7+AY7)</f>
+      <c r="K7" s="189">
+        <f t="shared" ref="K7:K10" si="28">AY7/(AF7+AP7+BM7+AZ7+AY7)</f>
         <v>0.17718424342566261</v>
       </c>
-      <c r="L7" s="250">
-        <f t="shared" ref="L7:L10" si="30">BL7/(AE7+AO7+BL7+AY7)</f>
+      <c r="L7" s="191">
+        <f t="shared" ref="L7:L10" si="29">BL7/(AE7+AO7+BL7+AY7)</f>
         <v>0.63712533271612082</v>
       </c>
       <c r="M7" s="154">
-        <f t="shared" ref="M7:M10" si="31">(S7+T7)*I7</f>
+        <f t="shared" ref="M7:M10" si="30">(S7+T7)*I7</f>
         <v>1817.529622343093</v>
       </c>
       <c r="N7" s="154">
-        <f t="shared" ref="N7:N10" si="32">(S7+T7)*J7</f>
+        <f t="shared" ref="N7:N10" si="31">(S7+T7)*J7</f>
         <v>4842.3334413455232</v>
       </c>
       <c r="O7" s="154">
-        <f t="shared" ref="O7:O10" si="33">(S7+T7)*K7</f>
+        <f t="shared" ref="O7:O10" si="32">(S7+T7)*K7</f>
         <v>5241.1985126528125</v>
       </c>
       <c r="P7" s="154">
-        <f t="shared" ref="P7:P10" si="34">(S7+T7)*L7</f>
+        <f t="shared" ref="P7:P10" si="33">(S7+T7)*L7</f>
         <v>18846.485904409212</v>
       </c>
-      <c r="Q7" s="245">
+      <c r="Q7" s="186">
         <f>Q6+1</f>
         <v>46023</v>
       </c>
@@ -8112,132 +8114,133 @@
       <c r="AA7" s="141">
         <v>0</v>
       </c>
-      <c r="AB7" s="245">
+      <c r="AB7" s="186">
         <f>AB6+1</f>
         <v>46023</v>
       </c>
-      <c r="AC7" s="251">
-        <f t="shared" ref="AC7:AC10" si="35">+AF7/AE7</f>
+      <c r="AC7" s="192">
+        <f t="shared" ref="AC7:AC10" si="34">+AF7/AE7</f>
         <v>1</v>
       </c>
-      <c r="AD7" s="252">
-        <f t="shared" ref="AD7:AD10" si="36">+AG7/AE7</f>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="253">
+      <c r="AD7" s="193">
+        <f t="shared" ref="AD7:AD10" si="35">+AG7/AE7</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="194">
         <v>1991</v>
       </c>
-      <c r="AF7" s="254">
-        <f t="shared" ref="AF7:AF36" si="37">+AE7-AG7</f>
+      <c r="AF7" s="195">
+        <f t="shared" ref="AF7:AF36" si="36">+AE7-AG7</f>
         <v>1991</v>
       </c>
       <c r="AG7" s="154">
         <v>0</v>
       </c>
-      <c r="AH7" s="255">
+      <c r="AH7" s="196">
         <v>1451.33</v>
       </c>
       <c r="AI7" s="156">
         <v>0.69166666666666665</v>
       </c>
-      <c r="AJ7" s="255">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="256">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="245">
-        <f t="shared" ref="AL7:AL37" si="38">AL6+1</f>
+      <c r="AJ7" s="196">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="197">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="186">
+        <f t="shared" ref="AL7:AL37" si="37">AL6+1</f>
         <v>46023</v>
       </c>
-      <c r="AM7" s="257">
-        <f t="shared" ref="AM7:AM10" si="39">+AP7/AO7</f>
+      <c r="AM7" s="198">
+        <f t="shared" ref="AM7:AM10" si="38">+AP7/AO7</f>
         <v>0.29865585823357521</v>
       </c>
-      <c r="AN7" s="251">
-        <f t="shared" ref="AN7:AN10" si="40">+AQ7/AO7</f>
+      <c r="AN7" s="192">
+        <f t="shared" ref="AN7:AN10" si="39">+AQ7/AO7</f>
         <v>0.70134414176642479</v>
       </c>
-      <c r="AO7" s="258">
+      <c r="AO7" s="199">
         <v>5304.5</v>
       </c>
-      <c r="AP7" s="259">
-        <f t="shared" ref="AP7:AP36" si="41">AO7-AQ7</f>
+      <c r="AP7" s="200">
+        <f t="shared" ref="AP7:AP36" si="40">AO7-AQ7</f>
         <v>1584.2199999999998</v>
       </c>
-      <c r="AQ7" s="260">
+      <c r="AQ7" s="201">
         <v>3720.28</v>
       </c>
-      <c r="AR7" s="255">
+      <c r="AR7" s="196">
         <v>2057.79</v>
       </c>
-      <c r="AS7" s="261">
+      <c r="AS7" s="202">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AT7" s="255">
+      <c r="AT7" s="196">
         <v>170.65</v>
       </c>
-      <c r="AU7" s="262">
+      <c r="AU7" s="203">
         <v>0.28125</v>
       </c>
-      <c r="AV7" s="245">
+      <c r="AV7" s="186">
         <f>AV6+1</f>
         <v>46023</v>
       </c>
-      <c r="AW7" s="263">
-        <f t="shared" ref="AW7:AW10" si="42">BA7/AZ7</f>
-        <v>0.40963253416984091</v>
-      </c>
-      <c r="AX7" s="263">
-        <f t="shared" ref="AX7:AX10" si="43">BB7/AZ7</f>
-        <v>0.59036746583015909</v>
-      </c>
-      <c r="AY7" s="264">
-        <f t="shared" ref="AY7:AY36" si="44">BA7+BB7</f>
+      <c r="AW7" s="204">
+        <f t="shared" ref="AW7:AW10" si="41">BA7/AZ7</f>
+        <v>0.29827246246919115</v>
+      </c>
+      <c r="AX7" s="204">
+        <f t="shared" ref="AX7:AX10" si="42">BB7/AZ7</f>
+        <v>0.70172753753080885</v>
+      </c>
+      <c r="AY7" s="205">
+        <f t="shared" ref="AY7:AY36" si="43">BA7+BB7</f>
         <v>4463</v>
       </c>
-      <c r="AZ7" s="265">
+      <c r="AZ7" s="206">
         <v>4463</v>
       </c>
-      <c r="BA7" s="266">
-        <f t="shared" ref="BA7:BA13" si="45">AZ7-BB7</f>
-        <v>1828.19</v>
-      </c>
-      <c r="BB7" s="264">
-        <v>2634.81</v>
-      </c>
-      <c r="BC7" s="265">
+      <c r="BA7" s="207">
+        <f t="shared" ref="BA7:BA13" si="44">AZ7-BB7</f>
+        <v>1331.19</v>
+      </c>
+      <c r="BB7" s="205">
+        <f>2634.81+497</f>
+        <v>3131.81</v>
+      </c>
+      <c r="BC7" s="206">
         <v>2005.46</v>
       </c>
-      <c r="BD7" s="267">
+      <c r="BD7" s="208">
         <v>0.72916666666666663</v>
       </c>
-      <c r="BE7" s="268">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="267">
-        <v>0</v>
-      </c>
-      <c r="BG7" s="268">
+      <c r="BE7" s="209">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="208">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="209">
         <v>150.82</v>
       </c>
-      <c r="BH7" s="267">
+      <c r="BH7" s="208">
         <v>0.90625</v>
       </c>
-      <c r="BI7" s="245">
+      <c r="BI7" s="186">
         <f>BI6+1</f>
         <v>46023</v>
       </c>
-      <c r="BJ7" s="269">
-        <f t="shared" ref="BJ7:BJ10" si="46">+BM7/BL7</f>
+      <c r="BJ7" s="210">
+        <f t="shared" ref="BJ7:BJ10" si="45">+BM7/BL7</f>
         <v>0.6145360312904905</v>
       </c>
-      <c r="BK7" s="251">
-        <f t="shared" ref="BK7:BK10" si="47">+BN7/BL7</f>
+      <c r="BK7" s="192">
+        <f t="shared" ref="BK7:BK10" si="46">+BN7/BL7</f>
         <v>0.38546396870950944</v>
       </c>
-      <c r="BL7" s="270">
-        <f t="shared" ref="BL7:BL10" si="48">BM7+BN7</f>
+      <c r="BL7" s="211">
+        <f t="shared" ref="BL7:BL10" si="47">BM7+BN7</f>
         <v>20645.25</v>
       </c>
       <c r="BM7" s="154">
@@ -8258,11 +8261,12 @@
       <c r="BR7" s="156">
         <v>0.41875000000000001</v>
       </c>
+      <c r="BU7" s="267"/>
     </row>
-    <row r="8" spans="1:71" s="13" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:73" s="13" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="165"/>
       <c r="B8" s="56">
-        <f t="shared" ref="B8:B37" si="49">B7+1</f>
+        <f t="shared" ref="B8:B37" si="48">B7+1</f>
         <v>46024</v>
       </c>
       <c r="C8" s="163"/>
@@ -8272,84 +8276,84 @@
       </c>
       <c r="E8" s="158">
         <f t="shared" si="23"/>
-        <v>0.8735126644413902</v>
+        <v>0.86375417239348129</v>
       </c>
       <c r="F8" s="87">
         <f t="shared" si="24"/>
-        <v>44488</v>
+        <v>43991</v>
       </c>
       <c r="G8" s="158">
         <f t="shared" si="25"/>
-        <v>0.12648733555860986</v>
-      </c>
-      <c r="H8" s="145">
+        <v>0.13624582760651874</v>
+      </c>
+      <c r="H8" s="269">
+        <f t="shared" ref="H8:H36" si="49">U8+AG8+AQ8+BB8</f>
+        <v>6939</v>
+      </c>
+      <c r="I8" s="159">
         <f t="shared" si="26"/>
-        <v>6442</v>
-      </c>
-      <c r="I8" s="159">
+        <v>0.11432397667001462</v>
+      </c>
+      <c r="J8" s="158">
         <f t="shared" si="27"/>
-        <v>0.11432397667001462</v>
-      </c>
-      <c r="J8" s="158">
+        <v>0.15619108033338619</v>
+      </c>
+      <c r="K8" s="158">
         <f t="shared" si="28"/>
-        <v>0.15619108033338619</v>
-      </c>
-      <c r="K8" s="158">
+        <v>0.16645385468779436</v>
+      </c>
+      <c r="L8" s="160">
         <f t="shared" si="29"/>
-        <v>0.16645385468779436</v>
-      </c>
-      <c r="L8" s="160">
+        <v>0.5893640640693556</v>
+      </c>
+      <c r="M8" s="145">
         <f t="shared" si="30"/>
-        <v>0.5893640640693556</v>
-      </c>
-      <c r="M8" s="145">
+        <v>5662.2379165124839</v>
+      </c>
+      <c r="N8" s="145">
         <f t="shared" si="31"/>
-        <v>5662.2379165124839</v>
-      </c>
-      <c r="N8" s="145">
+        <v>7735.8318267519508</v>
+      </c>
+      <c r="O8" s="145">
         <f t="shared" si="32"/>
-        <v>7735.8318267519508</v>
-      </c>
-      <c r="O8" s="145">
+        <v>8244.1265149770788</v>
+      </c>
+      <c r="P8" s="145">
         <f t="shared" si="33"/>
-        <v>8244.1265149770788</v>
-      </c>
-      <c r="P8" s="145">
-        <f t="shared" si="34"/>
         <v>29190.023365227044</v>
       </c>
       <c r="Q8" s="56">
         <f t="shared" ref="Q8:Q37" si="50">Q7+1</f>
         <v>46024</v>
       </c>
-      <c r="R8" s="308">
+      <c r="R8" s="249">
         <v>50930</v>
       </c>
-      <c r="S8" s="309">
-        <v>0</v>
-      </c>
-      <c r="T8" s="309">
+      <c r="S8" s="250">
+        <v>0</v>
+      </c>
+      <c r="T8" s="250">
         <v>49528</v>
       </c>
-      <c r="U8" s="309">
-        <v>0</v>
-      </c>
-      <c r="V8" s="310">
+      <c r="U8" s="250">
+        <v>0</v>
+      </c>
+      <c r="V8" s="251">
         <v>13771</v>
       </c>
-      <c r="W8" s="311">
+      <c r="W8" s="252">
         <v>0.36458333333333331</v>
       </c>
-      <c r="X8" s="310">
+      <c r="X8" s="251">
         <v>4226</v>
       </c>
-      <c r="Y8" s="311">
+      <c r="Y8" s="252">
         <v>0.78125</v>
       </c>
-      <c r="Z8" s="310">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="311">
+      <c r="Z8" s="251">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="252">
         <v>0</v>
       </c>
       <c r="AB8" s="56">
@@ -8357,67 +8361,67 @@
         <v>46024</v>
       </c>
       <c r="AC8" s="76">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="AD8" s="161">
         <f t="shared" si="35"/>
-        <v>1</v>
-      </c>
-      <c r="AD8" s="161">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="253">
+        <v>6488</v>
+      </c>
+      <c r="AF8" s="118">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="312">
         <v>6488</v>
       </c>
-      <c r="AF8" s="118">
+      <c r="AG8" s="145">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="254">
+        <v>3502</v>
+      </c>
+      <c r="AI8" s="255">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="AJ8" s="254">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="256">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="56">
         <f t="shared" si="37"/>
-        <v>6488</v>
-      </c>
-      <c r="AG8" s="145">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="313">
-        <v>3502</v>
-      </c>
-      <c r="AI8" s="314">
-        <v>0.72777777777777775</v>
-      </c>
-      <c r="AJ8" s="313">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="315">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="56">
+        <v>46024</v>
+      </c>
+      <c r="AM8" s="77">
         <f t="shared" si="38"/>
-        <v>46024</v>
-      </c>
-      <c r="AM8" s="77">
+        <v>0.5703971119133574</v>
+      </c>
+      <c r="AN8" s="76">
         <f t="shared" si="39"/>
-        <v>0.5703971119133574</v>
-      </c>
-      <c r="AN8" s="76">
+        <v>0.4296028880866426</v>
+      </c>
+      <c r="AO8" s="257">
+        <v>8864</v>
+      </c>
+      <c r="AP8" s="117">
         <f t="shared" si="40"/>
-        <v>0.4296028880866426</v>
-      </c>
-      <c r="AO8" s="316">
-        <v>8864</v>
-      </c>
-      <c r="AP8" s="117">
-        <f t="shared" si="41"/>
         <v>5056</v>
       </c>
-      <c r="AQ8" s="317">
+      <c r="AQ8" s="258">
         <v>3808</v>
       </c>
-      <c r="AR8" s="313">
+      <c r="AR8" s="254">
         <v>3358</v>
       </c>
-      <c r="AS8" s="318">
+      <c r="AS8" s="259">
         <v>0.71388888888888891</v>
       </c>
-      <c r="AT8" s="313">
+      <c r="AT8" s="254">
         <v>188.24</v>
       </c>
-      <c r="AU8" s="319">
+      <c r="AU8" s="260">
         <v>0.28125</v>
       </c>
       <c r="AV8" s="56">
@@ -8425,43 +8429,44 @@
         <v>46024</v>
       </c>
       <c r="AW8" s="110">
+        <f t="shared" si="41"/>
+        <v>0.60626257545271633</v>
+      </c>
+      <c r="AX8" s="110">
         <f t="shared" si="42"/>
-        <v>0.66876257545271633</v>
-      </c>
-      <c r="AX8" s="110">
+        <v>0.39373742454728372</v>
+      </c>
+      <c r="AY8" s="261">
         <f t="shared" si="43"/>
-        <v>0.33123742454728372</v>
-      </c>
-      <c r="AY8" s="320">
+        <v>7952</v>
+      </c>
+      <c r="AZ8" s="262">
+        <v>7952</v>
+      </c>
+      <c r="BA8" s="120">
         <f t="shared" si="44"/>
-        <v>7952</v>
-      </c>
-      <c r="AZ8" s="321">
-        <v>7952</v>
-      </c>
-      <c r="BA8" s="120">
-        <f t="shared" si="45"/>
-        <v>5318</v>
-      </c>
-      <c r="BB8" s="320">
-        <v>2634</v>
-      </c>
-      <c r="BC8" s="321">
+        <v>4821</v>
+      </c>
+      <c r="BB8" s="261">
+        <f>2634+497</f>
+        <v>3131</v>
+      </c>
+      <c r="BC8" s="262">
         <v>3223</v>
       </c>
-      <c r="BD8" s="322">
+      <c r="BD8" s="263">
         <v>0.71875</v>
       </c>
       <c r="BE8" s="105">
         <v>0</v>
       </c>
-      <c r="BF8" s="322">
+      <c r="BF8" s="263">
         <v>0</v>
       </c>
       <c r="BG8" s="105">
         <v>156</v>
       </c>
-      <c r="BH8" s="322">
+      <c r="BH8" s="263">
         <v>0.90625</v>
       </c>
       <c r="BI8" s="56">
@@ -8469,15 +8474,15 @@
         <v>46024</v>
       </c>
       <c r="BJ8" s="78">
+        <f t="shared" si="45"/>
+        <v>0.60767781863844295</v>
+      </c>
+      <c r="BK8" s="76">
         <f t="shared" si="46"/>
-        <v>0.60767781863844295</v>
-      </c>
-      <c r="BK8" s="76">
+        <v>0.39232218136155711</v>
+      </c>
+      <c r="BL8" s="79">
         <f t="shared" si="47"/>
-        <v>0.39232218136155711</v>
-      </c>
-      <c r="BL8" s="79">
-        <f t="shared" si="48"/>
         <v>33447</v>
       </c>
       <c r="BM8" s="145">
@@ -8486,321 +8491,324 @@
       <c r="BN8" s="145">
         <v>13122</v>
       </c>
-      <c r="BO8" s="323">
+      <c r="BO8" s="264">
         <v>4111</v>
       </c>
-      <c r="BP8" s="314">
+      <c r="BP8" s="255">
         <v>0.73958333333333337</v>
       </c>
-      <c r="BQ8" s="324">
+      <c r="BQ8" s="265">
         <v>2752</v>
       </c>
-      <c r="BR8" s="314">
+      <c r="BR8" s="255">
         <v>0.73958333333333337</v>
       </c>
+      <c r="BU8" s="267"/>
     </row>
-    <row r="9" spans="1:71" s="307" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="272" t="s">
+    <row r="9" spans="1:73" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="213" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="273">
-        <f t="shared" si="49"/>
+      <c r="B9" s="214">
+        <f t="shared" si="48"/>
         <v>46025</v>
       </c>
-      <c r="C9" s="274"/>
-      <c r="D9" s="275">
+      <c r="C9" s="215"/>
+      <c r="D9" s="216">
         <f t="shared" si="22"/>
         <v>32846</v>
       </c>
-      <c r="E9" s="276">
+      <c r="E9" s="217">
         <f t="shared" si="23"/>
-        <v>0.80980941362723013</v>
-      </c>
-      <c r="F9" s="275">
+        <v>0.79467819521402916</v>
+      </c>
+      <c r="F9" s="216">
         <f t="shared" si="24"/>
-        <v>26599</v>
-      </c>
-      <c r="G9" s="276">
+        <v>26102</v>
+      </c>
+      <c r="G9" s="217">
         <f t="shared" si="25"/>
-        <v>0.19019058637276989</v>
-      </c>
-      <c r="H9" s="277">
+        <v>0.2053218047859709</v>
+      </c>
+      <c r="H9" s="270">
+        <f t="shared" si="49"/>
+        <v>6744</v>
+      </c>
+      <c r="I9" s="219">
         <f t="shared" si="26"/>
-        <v>6247</v>
-      </c>
-      <c r="I9" s="278">
+        <v>7.755652868434823E-2</v>
+      </c>
+      <c r="J9" s="217">
         <f t="shared" si="27"/>
-        <v>7.755652868434823E-2</v>
-      </c>
-      <c r="J9" s="276">
+        <v>0.15684816436696136</v>
+      </c>
+      <c r="K9" s="217">
         <f t="shared" si="28"/>
-        <v>0.15684816436696136</v>
-      </c>
-      <c r="K9" s="276">
+        <v>0.16607400626694363</v>
+      </c>
+      <c r="L9" s="220">
         <f t="shared" si="29"/>
-        <v>0.16607400626694363</v>
-      </c>
-      <c r="L9" s="279">
+        <v>0.6356826131262221</v>
+      </c>
+      <c r="M9" s="218">
         <f t="shared" si="30"/>
-        <v>0.6356826131262221</v>
-      </c>
-      <c r="M9" s="277">
+        <v>2430.3889393814206</v>
+      </c>
+      <c r="N9" s="218">
         <f t="shared" si="31"/>
-        <v>2430.3889393814206</v>
-      </c>
-      <c r="N9" s="277">
+        <v>4915.1509267674683</v>
+      </c>
+      <c r="O9" s="218">
         <f t="shared" si="32"/>
-        <v>4915.1509267674683</v>
-      </c>
-      <c r="O9" s="277">
+        <v>5204.2611343872122</v>
+      </c>
+      <c r="P9" s="218">
         <f t="shared" si="33"/>
-        <v>5204.2611343872122</v>
-      </c>
-      <c r="P9" s="277">
-        <f t="shared" si="34"/>
         <v>19920.386047536424</v>
       </c>
-      <c r="Q9" s="273">
+      <c r="Q9" s="214">
         <f t="shared" si="50"/>
         <v>46025</v>
       </c>
-      <c r="R9" s="280">
+      <c r="R9" s="221">
         <v>32846</v>
       </c>
-      <c r="S9" s="281">
-        <v>0</v>
-      </c>
-      <c r="T9" s="281">
+      <c r="S9" s="222">
+        <v>0</v>
+      </c>
+      <c r="T9" s="222">
         <v>31337</v>
       </c>
-      <c r="U9" s="281">
-        <v>0</v>
-      </c>
-      <c r="V9" s="282">
+      <c r="U9" s="222">
+        <v>0</v>
+      </c>
+      <c r="V9" s="223">
         <v>6876</v>
       </c>
-      <c r="W9" s="283">
+      <c r="W9" s="224">
         <v>0.82291666666666663</v>
       </c>
-      <c r="X9" s="282">
+      <c r="X9" s="223">
         <v>2108</v>
       </c>
-      <c r="Y9" s="283">
+      <c r="Y9" s="224">
         <v>0.84375</v>
       </c>
-      <c r="Z9" s="282">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="283">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="273">
+      <c r="Z9" s="223">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="224">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="214">
         <f t="shared" si="51"/>
         <v>46025</v>
       </c>
-      <c r="AC9" s="284">
+      <c r="AC9" s="225">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="AD9" s="226">
         <f t="shared" si="35"/>
-        <v>1</v>
-      </c>
-      <c r="AD9" s="285">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="227">
+        <v>2816</v>
+      </c>
+      <c r="AF9" s="228">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AE9" s="286">
         <v>2816</v>
       </c>
-      <c r="AF9" s="287">
+      <c r="AG9" s="218">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="229">
+        <v>1731</v>
+      </c>
+      <c r="AI9" s="230">
+        <v>0.93819444444444444</v>
+      </c>
+      <c r="AJ9" s="229">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="231">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="214">
         <f t="shared" si="37"/>
-        <v>2816</v>
-      </c>
-      <c r="AG9" s="277">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="288">
-        <v>1731</v>
-      </c>
-      <c r="AI9" s="289">
-        <v>0.93819444444444444</v>
-      </c>
-      <c r="AJ9" s="288">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="290">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="273">
+        <v>46025</v>
+      </c>
+      <c r="AM9" s="232">
         <f t="shared" si="38"/>
-        <v>46025</v>
-      </c>
-      <c r="AM9" s="291">
+        <v>0.3592625109745391</v>
+      </c>
+      <c r="AN9" s="225">
         <f t="shared" si="39"/>
-        <v>0.3592625109745391</v>
-      </c>
-      <c r="AN9" s="284">
+        <v>0.6407374890254609</v>
+      </c>
+      <c r="AO9" s="233">
+        <v>5695</v>
+      </c>
+      <c r="AP9" s="234">
         <f t="shared" si="40"/>
-        <v>0.6407374890254609</v>
-      </c>
-      <c r="AO9" s="292">
-        <v>5695</v>
-      </c>
-      <c r="AP9" s="293">
-        <f t="shared" si="41"/>
         <v>2046</v>
       </c>
-      <c r="AQ9" s="294">
+      <c r="AQ9" s="235">
         <v>3649</v>
       </c>
-      <c r="AR9" s="288">
+      <c r="AR9" s="229">
         <v>1594</v>
       </c>
-      <c r="AS9" s="295">
+      <c r="AS9" s="236">
         <v>0.95138888888888884</v>
       </c>
-      <c r="AT9" s="288">
+      <c r="AT9" s="229">
         <v>176</v>
       </c>
-      <c r="AU9" s="296">
+      <c r="AU9" s="237">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="AV9" s="273">
+      <c r="AV9" s="214">
         <f t="shared" si="52"/>
         <v>46025</v>
       </c>
-      <c r="AW9" s="297">
+      <c r="AW9" s="238">
+        <f t="shared" si="41"/>
+        <v>0.34386262454950178</v>
+      </c>
+      <c r="AX9" s="238">
         <f t="shared" si="42"/>
-        <v>0.44922620309518763</v>
-      </c>
-      <c r="AX9" s="297">
+        <v>0.65613737545049822</v>
+      </c>
+      <c r="AY9" s="239">
         <f t="shared" si="43"/>
-        <v>0.55077379690481243</v>
-      </c>
-      <c r="AY9" s="298">
+        <v>4717</v>
+      </c>
+      <c r="AZ9" s="240">
+        <v>4717</v>
+      </c>
+      <c r="BA9" s="241">
         <f t="shared" si="44"/>
-        <v>4717</v>
-      </c>
-      <c r="AZ9" s="299">
-        <v>4717</v>
-      </c>
-      <c r="BA9" s="300">
-        <f t="shared" si="45"/>
-        <v>2119</v>
-      </c>
-      <c r="BB9" s="298">
-        <v>2598</v>
-      </c>
-      <c r="BC9" s="299">
+        <v>1622</v>
+      </c>
+      <c r="BB9" s="239">
+        <f>2598+497</f>
+        <v>3095</v>
+      </c>
+      <c r="BC9" s="240">
         <v>1436</v>
       </c>
-      <c r="BD9" s="301">
+      <c r="BD9" s="242">
         <v>0.78125</v>
       </c>
-      <c r="BE9" s="302">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="301">
-        <v>0</v>
-      </c>
-      <c r="BG9" s="302">
+      <c r="BE9" s="243">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="242">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="243">
         <v>158</v>
       </c>
-      <c r="BH9" s="301">
+      <c r="BH9" s="242">
         <v>0.92708333333333337</v>
       </c>
-      <c r="BI9" s="273">
+      <c r="BI9" s="214">
         <f t="shared" si="53"/>
         <v>46025</v>
       </c>
-      <c r="BJ9" s="303">
+      <c r="BJ9" s="244">
+        <f t="shared" si="45"/>
+        <v>0.61119535548719728</v>
+      </c>
+      <c r="BK9" s="225">
         <f t="shared" si="46"/>
-        <v>0.61119535548719728</v>
-      </c>
-      <c r="BK9" s="284">
+        <v>0.38880464451280272</v>
+      </c>
+      <c r="BL9" s="245">
         <f t="shared" si="47"/>
-        <v>0.38880464451280272</v>
-      </c>
-      <c r="BL9" s="304">
+        <v>23081</v>
+      </c>
+      <c r="BM9" s="218">
+        <v>14107</v>
+      </c>
+      <c r="BN9" s="218">
+        <v>8974</v>
+      </c>
+      <c r="BO9" s="246">
+        <v>3133</v>
+      </c>
+      <c r="BP9" s="230" t="s">
+        <v>69</v>
+      </c>
+      <c r="BQ9" s="247">
+        <v>2054</v>
+      </c>
+      <c r="BR9" s="230">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="BU9" s="267"/>
+    </row>
+    <row r="10" spans="1:73" s="212" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="185"/>
+      <c r="B10" s="186">
         <f t="shared" si="48"/>
-        <v>23081</v>
-      </c>
-      <c r="BM9" s="277">
-        <v>14107</v>
-      </c>
-      <c r="BN9" s="277">
-        <v>8974</v>
-      </c>
-      <c r="BO9" s="305">
-        <v>3133</v>
-      </c>
-      <c r="BP9" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="BQ9" s="306">
-        <v>2054</v>
-      </c>
-      <c r="BR9" s="289">
-        <v>0.79513888888888884</v>
-      </c>
-    </row>
-    <row r="10" spans="1:71" s="271" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="244"/>
-      <c r="B10" s="245">
-        <f t="shared" si="49"/>
         <v>46026</v>
       </c>
-      <c r="C10" s="325"/>
-      <c r="D10" s="247">
+      <c r="C10" s="266"/>
+      <c r="D10" s="188">
         <f t="shared" si="22"/>
         <v>27816</v>
       </c>
-      <c r="E10" s="248">
+      <c r="E10" s="189">
         <f t="shared" si="23"/>
-        <v>0.76053350589588731</v>
-      </c>
-      <c r="F10" s="247">
+        <v>0.74266609145815354</v>
+      </c>
+      <c r="F10" s="188">
         <f t="shared" si="24"/>
-        <v>21155</v>
-      </c>
-      <c r="G10" s="248">
+        <v>20658</v>
+      </c>
+      <c r="G10" s="189">
         <f t="shared" si="25"/>
-        <v>0.23946649410411275</v>
-      </c>
-      <c r="H10" s="154">
+        <v>0.2573339085418464</v>
+      </c>
+      <c r="H10" s="268">
+        <f t="shared" si="49"/>
+        <v>7158</v>
+      </c>
+      <c r="I10" s="190">
         <f t="shared" si="26"/>
-        <v>6661</v>
-      </c>
-      <c r="I10" s="249">
+        <v>6.4624838933491927E-2</v>
+      </c>
+      <c r="J10" s="189">
         <f t="shared" si="27"/>
-        <v>6.4624838933491927E-2</v>
-      </c>
-      <c r="J10" s="248">
+        <v>0.17127564674397858</v>
+      </c>
+      <c r="K10" s="189">
         <f t="shared" si="28"/>
-        <v>0.17127564674397858</v>
-      </c>
-      <c r="K10" s="248">
+        <v>0.18432382238730374</v>
+      </c>
+      <c r="L10" s="191">
         <f t="shared" si="29"/>
-        <v>0.18432382238730374</v>
-      </c>
-      <c r="L10" s="250">
+        <v>0.6198169623682559</v>
+      </c>
+      <c r="M10" s="154">
         <f t="shared" si="30"/>
-        <v>0.6198169623682559</v>
-      </c>
-      <c r="M10" s="154">
+        <v>1717.3404698186146</v>
+      </c>
+      <c r="N10" s="154">
         <f t="shared" si="31"/>
-        <v>1717.3404698186146</v>
-      </c>
-      <c r="N10" s="154">
+        <v>4551.4790365744866</v>
+      </c>
+      <c r="O10" s="154">
         <f t="shared" si="32"/>
-        <v>4551.4790365744866</v>
-      </c>
-      <c r="O10" s="154">
+        <v>4898.2212561202095</v>
+      </c>
+      <c r="P10" s="154">
         <f t="shared" si="33"/>
-        <v>4898.2212561202095</v>
-      </c>
-      <c r="P10" s="154">
-        <f t="shared" si="34"/>
         <v>16471.015957974032</v>
       </c>
-      <c r="Q10" s="245">
+      <c r="Q10" s="186">
         <f t="shared" si="50"/>
         <v>46026</v>
       </c>
@@ -8834,133 +8842,133 @@
       <c r="AA10" s="141">
         <v>0</v>
       </c>
-      <c r="AB10" s="245">
+      <c r="AB10" s="186">
         <f t="shared" si="51"/>
         <v>46026</v>
       </c>
-      <c r="AC10" s="251">
+      <c r="AC10" s="192">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="AD10" s="193">
         <f t="shared" si="35"/>
-        <v>1</v>
-      </c>
-      <c r="AD10" s="252">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="194">
+        <v>1956</v>
+      </c>
+      <c r="AF10" s="195">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="253">
         <v>1956</v>
       </c>
-      <c r="AF10" s="254">
-        <f t="shared" si="37"/>
-        <v>1956</v>
-      </c>
       <c r="AG10" s="154">
         <v>0</v>
       </c>
-      <c r="AH10" s="255">
+      <c r="AH10" s="196">
         <v>1393</v>
       </c>
       <c r="AI10" s="156">
         <v>0.93125000000000002</v>
       </c>
-      <c r="AJ10" s="255">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="256">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="245">
+      <c r="AJ10" s="196">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="197">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="186">
+        <f t="shared" si="37"/>
+        <v>46026</v>
+      </c>
+      <c r="AM10" s="198">
         <f t="shared" si="38"/>
-        <v>46026</v>
-      </c>
-      <c r="AM10" s="257">
+        <v>0.30266203703703703</v>
+      </c>
+      <c r="AN10" s="192">
         <f t="shared" si="39"/>
-        <v>0.30266203703703703</v>
-      </c>
-      <c r="AN10" s="251">
+        <v>0.69733796296296291</v>
+      </c>
+      <c r="AO10" s="199">
+        <v>5184</v>
+      </c>
+      <c r="AP10" s="200">
         <f t="shared" si="40"/>
-        <v>0.69733796296296291</v>
-      </c>
-      <c r="AO10" s="258">
-        <v>5184</v>
-      </c>
-      <c r="AP10" s="259">
-        <f t="shared" si="41"/>
         <v>1569</v>
       </c>
-      <c r="AQ10" s="260">
+      <c r="AQ10" s="201">
         <v>3615</v>
       </c>
-      <c r="AR10" s="255">
+      <c r="AR10" s="196">
         <v>1500</v>
       </c>
-      <c r="AS10" s="261">
+      <c r="AS10" s="202">
         <v>0.68194444444444446</v>
       </c>
-      <c r="AT10" s="255">
+      <c r="AT10" s="196">
         <v>169</v>
       </c>
-      <c r="AU10" s="262">
+      <c r="AU10" s="203">
         <v>0.92708333333333337</v>
       </c>
-      <c r="AV10" s="245">
+      <c r="AV10" s="186">
         <f t="shared" si="52"/>
         <v>46026</v>
       </c>
-      <c r="AW10" s="263">
+      <c r="AW10" s="204">
+        <f t="shared" si="41"/>
+        <v>0.18868788642088391</v>
+      </c>
+      <c r="AX10" s="204">
         <f t="shared" si="42"/>
-        <v>0.30249599267231508</v>
-      </c>
-      <c r="AX10" s="263">
+        <v>0.81131211357911615</v>
+      </c>
+      <c r="AY10" s="205">
         <f t="shared" si="43"/>
-        <v>0.69750400732768492</v>
-      </c>
-      <c r="AY10" s="264">
+        <v>4367</v>
+      </c>
+      <c r="AZ10" s="206">
+        <v>4367</v>
+      </c>
+      <c r="BA10" s="207">
         <f t="shared" si="44"/>
-        <v>4367</v>
-      </c>
-      <c r="AZ10" s="265">
-        <v>4367</v>
-      </c>
-      <c r="BA10" s="266">
-        <f t="shared" si="45"/>
-        <v>1321</v>
-      </c>
-      <c r="BB10" s="264">
-        <f>1319+1727</f>
-        <v>3046</v>
-      </c>
-      <c r="BC10" s="265">
+        <v>824</v>
+      </c>
+      <c r="BB10" s="205">
+        <f>1319+1727+497</f>
+        <v>3543</v>
+      </c>
+      <c r="BC10" s="206">
         <v>1773</v>
       </c>
-      <c r="BD10" s="267">
+      <c r="BD10" s="208">
         <v>0.40625</v>
       </c>
-      <c r="BE10" s="268">
-        <v>0</v>
-      </c>
-      <c r="BF10" s="267">
-        <v>0</v>
-      </c>
-      <c r="BG10" s="268">
+      <c r="BE10" s="209">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="208">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="209">
         <v>157</v>
       </c>
-      <c r="BH10" s="267">
+      <c r="BH10" s="208">
         <v>0.88541666666666663</v>
       </c>
-      <c r="BI10" s="245">
+      <c r="BI10" s="186">
         <f t="shared" si="53"/>
         <v>46026</v>
       </c>
-      <c r="BJ10" s="269">
+      <c r="BJ10" s="210">
+        <f t="shared" si="45"/>
+        <v>0.60943496801705754</v>
+      </c>
+      <c r="BK10" s="192">
         <f t="shared" si="46"/>
-        <v>0.60943496801705754</v>
-      </c>
-      <c r="BK10" s="251">
+        <v>0.39056503198294246</v>
+      </c>
+      <c r="BL10" s="211">
         <f t="shared" si="47"/>
-        <v>0.39056503198294246</v>
-      </c>
-      <c r="BL10" s="270">
-        <f t="shared" si="48"/>
         <v>18760</v>
       </c>
       <c r="BM10" s="154">
@@ -8981,13 +8989,14 @@
       <c r="BR10" s="156">
         <v>0.4375</v>
       </c>
-      <c r="BS10" s="271" t="s">
+      <c r="BS10" s="212" t="s">
         <v>68</v>
       </c>
+      <c r="BU10" s="267"/>
     </row>
-    <row r="11" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46027</v>
       </c>
       <c r="C11" s="163"/>
@@ -8997,19 +9006,19 @@
       </c>
       <c r="E11" s="158">
         <f t="shared" ref="E11:E24" si="54">F11/D11</f>
-        <v>0.87267513949163045</v>
+        <v>0.86304634221946686</v>
       </c>
       <c r="F11" s="87">
         <f t="shared" si="24"/>
-        <v>45044</v>
+        <v>44547</v>
       </c>
       <c r="G11" s="158">
         <f t="shared" ref="G11:G24" si="55">H11/D11</f>
-        <v>0.1273248605083695</v>
-      </c>
-      <c r="H11" s="145">
-        <f t="shared" si="26"/>
-        <v>6572</v>
+        <v>0.13695365778053317</v>
+      </c>
+      <c r="H11" s="269">
+        <f t="shared" si="49"/>
+        <v>7069</v>
       </c>
       <c r="I11" s="159">
         <f t="shared" ref="I11:I24" si="56">AE11/(AE11+AO11+BL11+AY11)</f>
@@ -9093,7 +9102,7 @@
         <v>6672</v>
       </c>
       <c r="AF11" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6672</v>
       </c>
       <c r="AG11" s="146">
@@ -9112,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="AL11" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46027</v>
       </c>
       <c r="AM11" s="77">
@@ -9127,7 +9136,7 @@
         <v>9163</v>
       </c>
       <c r="AP11" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5282</v>
       </c>
       <c r="AQ11" s="150">
@@ -9151,25 +9160,26 @@
       </c>
       <c r="AW11" s="110">
         <f t="shared" ref="AW11:AW25" si="68">BA11/AZ11</f>
-        <v>0.67070484581497802</v>
+        <v>0.60988742046010769</v>
       </c>
       <c r="AX11" s="110">
         <f t="shared" ref="AX11:AX25" si="69">BB11/AZ11</f>
-        <v>0.32929515418502203</v>
+        <v>0.39011257953989231</v>
       </c>
       <c r="AY11" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8172</v>
       </c>
       <c r="AZ11" s="112">
         <v>8172</v>
       </c>
       <c r="BA11" s="169">
-        <f t="shared" si="45"/>
-        <v>5481</v>
+        <f t="shared" si="44"/>
+        <v>4984</v>
       </c>
       <c r="BB11" s="113">
-        <v>2691</v>
+        <f>2691+497</f>
+        <v>3188</v>
       </c>
       <c r="BC11" s="112">
         <v>3517</v>
@@ -9223,10 +9233,11 @@
       <c r="BR11" s="156">
         <v>0.69374999999999998</v>
       </c>
+      <c r="BU11" s="267"/>
     </row>
-    <row r="12" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46028</v>
       </c>
       <c r="C12" s="163"/>
@@ -9236,19 +9247,19 @@
       </c>
       <c r="E12" s="158">
         <f t="shared" si="54"/>
-        <v>0.87651829290668237</v>
+        <v>0.86739936149132146</v>
       </c>
       <c r="F12" s="87">
         <f t="shared" si="24"/>
-        <v>47772</v>
+        <v>47275</v>
       </c>
       <c r="G12" s="158">
         <f>H12/D12</f>
-        <v>0.12348170709331768</v>
-      </c>
-      <c r="H12" s="145">
-        <f t="shared" si="26"/>
-        <v>6730</v>
+        <v>0.13260063850867859</v>
+      </c>
+      <c r="H12" s="269">
+        <f t="shared" si="49"/>
+        <v>7227</v>
       </c>
       <c r="I12" s="159">
         <f t="shared" si="56"/>
@@ -9332,7 +9343,7 @@
         <v>7173</v>
       </c>
       <c r="AF12" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7173</v>
       </c>
       <c r="AG12" s="146">
@@ -9351,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="AL12" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46028</v>
       </c>
       <c r="AM12" s="77">
@@ -9366,7 +9377,7 @@
         <v>10384</v>
       </c>
       <c r="AP12" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>6415</v>
       </c>
       <c r="AQ12" s="150">
@@ -9390,25 +9401,26 @@
       </c>
       <c r="AW12" s="110">
         <f t="shared" si="68"/>
-        <v>0.68062463851937538</v>
+        <v>0.62313475997686529</v>
       </c>
       <c r="AX12" s="110">
         <f t="shared" si="69"/>
-        <v>0.31937536148062462</v>
+        <v>0.37686524002313476</v>
       </c>
       <c r="AY12" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8645</v>
       </c>
       <c r="AZ12" s="112">
         <v>8645</v>
       </c>
       <c r="BA12" s="169">
-        <f t="shared" si="45"/>
-        <v>5884</v>
+        <f t="shared" si="44"/>
+        <v>5387</v>
       </c>
       <c r="BB12" s="113">
-        <v>2761</v>
+        <f>2761+497</f>
+        <v>3258</v>
       </c>
       <c r="BC12" s="112">
         <v>3920</v>
@@ -9462,10 +9474,11 @@
       <c r="BR12" s="156">
         <v>0.70972222222222225</v>
       </c>
+      <c r="BU12" s="267"/>
     </row>
-    <row r="13" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46029</v>
       </c>
       <c r="C13" s="163"/>
@@ -9475,19 +9488,19 @@
       </c>
       <c r="E13" s="158">
         <f t="shared" si="54"/>
-        <v>0.8745938561512332</v>
+        <v>0.86541869738591048</v>
       </c>
       <c r="F13" s="87">
         <f t="shared" si="24"/>
-        <v>47375</v>
+        <v>46878</v>
       </c>
       <c r="G13" s="158">
         <f t="shared" si="55"/>
-        <v>0.1254061438487668</v>
-      </c>
-      <c r="H13" s="145">
-        <f t="shared" si="26"/>
-        <v>6793</v>
+        <v>0.13458130261408949</v>
+      </c>
+      <c r="H13" s="269">
+        <f t="shared" si="49"/>
+        <v>7290</v>
       </c>
       <c r="I13" s="159">
         <f t="shared" si="56"/>
@@ -9571,7 +9584,7 @@
         <v>7389</v>
       </c>
       <c r="AF13" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7389</v>
       </c>
       <c r="AG13" s="146">
@@ -9590,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="AL13" s="167">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46029</v>
       </c>
       <c r="AM13" s="77">
@@ -9605,7 +9618,7 @@
         <v>8411</v>
       </c>
       <c r="AP13" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4398</v>
       </c>
       <c r="AQ13" s="150">
@@ -9629,25 +9642,26 @@
       </c>
       <c r="AW13" s="168">
         <f t="shared" si="68"/>
-        <v>0.67846402960906782</v>
+        <v>0.62098080037011338</v>
       </c>
       <c r="AX13" s="168">
         <f t="shared" si="69"/>
-        <v>0.32153597039093224</v>
+        <v>0.37901919962988667</v>
       </c>
       <c r="AY13" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8646</v>
       </c>
       <c r="AZ13" s="112">
         <v>8646</v>
       </c>
       <c r="BA13" s="169">
-        <f t="shared" si="45"/>
-        <v>5866</v>
+        <f t="shared" si="44"/>
+        <v>5369</v>
       </c>
       <c r="BB13" s="113">
-        <v>2780</v>
+        <f>2780+497</f>
+        <v>3277</v>
       </c>
       <c r="BC13" s="112">
         <v>4016</v>
@@ -9701,10 +9715,11 @@
       <c r="BR13" s="156">
         <v>0.77430555555555558</v>
       </c>
+      <c r="BU13" s="267"/>
     </row>
-    <row r="14" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46030</v>
       </c>
       <c r="C14" s="163"/>
@@ -9714,19 +9729,19 @@
       </c>
       <c r="E14" s="158">
         <f t="shared" si="54"/>
-        <v>0.87617721426215689</v>
+        <v>0.86707098098134783</v>
       </c>
       <c r="F14" s="87">
         <f t="shared" si="24"/>
-        <v>47820</v>
+        <v>47323</v>
       </c>
       <c r="G14" s="158">
         <f t="shared" si="55"/>
-        <v>0.12382278573784308</v>
-      </c>
-      <c r="H14" s="145">
-        <f t="shared" si="26"/>
-        <v>6758</v>
+        <v>0.1329290190186522</v>
+      </c>
+      <c r="H14" s="269">
+        <f t="shared" si="49"/>
+        <v>7255</v>
       </c>
       <c r="I14" s="159">
         <f t="shared" si="56"/>
@@ -9829,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="AL14" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46030</v>
       </c>
       <c r="AM14" s="77">
@@ -9868,14 +9883,14 @@
       </c>
       <c r="AW14" s="110">
         <f t="shared" si="68"/>
-        <v>0.695263043003711</v>
+        <v>0.64101724514298186</v>
       </c>
       <c r="AX14" s="110">
         <f t="shared" si="69"/>
-        <v>0.304736956996289</v>
+        <v>0.35898275485701814</v>
       </c>
       <c r="AY14" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9162</v>
       </c>
       <c r="AZ14" s="112">
@@ -9883,10 +9898,11 @@
       </c>
       <c r="BA14" s="169">
         <f t="shared" ref="BA14" si="75">AZ14-BB14</f>
-        <v>6370</v>
+        <v>5873</v>
       </c>
       <c r="BB14" s="113">
-        <v>2792</v>
+        <f>2792+497</f>
+        <v>3289</v>
       </c>
       <c r="BC14" s="112">
         <v>4220</v>
@@ -9940,10 +9956,11 @@
       <c r="BR14" s="156">
         <v>0.76875000000000004</v>
       </c>
+      <c r="BU14" s="267"/>
     </row>
-    <row r="15" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46031</v>
       </c>
       <c r="C15" s="163"/>
@@ -9953,19 +9970,19 @@
       </c>
       <c r="E15" s="158">
         <f t="shared" si="54"/>
-        <v>0.87751055159365454</v>
+        <v>0.86846892737592785</v>
       </c>
       <c r="F15" s="87">
         <f t="shared" si="24"/>
-        <v>48235</v>
+        <v>47738</v>
       </c>
       <c r="G15" s="158">
         <f t="shared" si="55"/>
-        <v>0.12248944840634551</v>
-      </c>
-      <c r="H15" s="145">
-        <f t="shared" si="26"/>
-        <v>6733</v>
+        <v>0.13153107262407218</v>
+      </c>
+      <c r="H15" s="269">
+        <f t="shared" si="49"/>
+        <v>7230</v>
       </c>
       <c r="I15" s="159">
         <f t="shared" si="56"/>
@@ -10049,7 +10066,7 @@
         <v>7164</v>
       </c>
       <c r="AF15" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7164</v>
       </c>
       <c r="AG15" s="146">
@@ -10068,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="AL15" s="167">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46031</v>
       </c>
       <c r="AM15" s="77">
@@ -10083,7 +10100,7 @@
         <v>9404</v>
       </c>
       <c r="AP15" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5472</v>
       </c>
       <c r="AQ15" s="150">
@@ -10107,14 +10124,14 @@
       </c>
       <c r="AW15" s="168">
         <f t="shared" si="68"/>
-        <v>0.6995279982836301</v>
+        <v>0.6462132589573053</v>
       </c>
       <c r="AX15" s="168">
         <f t="shared" si="69"/>
-        <v>0.3004720017163699</v>
+        <v>0.3537867410426947</v>
       </c>
       <c r="AY15" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9322</v>
       </c>
       <c r="AZ15" s="112">
@@ -10122,10 +10139,11 @@
       </c>
       <c r="BA15" s="169">
         <f t="shared" ref="BA15:BA25" si="76">AZ15-BB15</f>
-        <v>6521</v>
+        <v>6024</v>
       </c>
       <c r="BB15" s="113">
-        <v>2801</v>
+        <f>2801+497</f>
+        <v>3298</v>
       </c>
       <c r="BC15" s="112">
         <v>4579</v>
@@ -10179,287 +10197,290 @@
       <c r="BR15" s="156">
         <v>0.80277777777777781</v>
       </c>
+      <c r="BU15" s="267"/>
     </row>
-    <row r="16" spans="1:71" s="307" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="272"/>
-      <c r="B16" s="273">
-        <f t="shared" si="49"/>
+    <row r="16" spans="1:73" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="213"/>
+      <c r="B16" s="214">
+        <f t="shared" si="48"/>
         <v>46032</v>
       </c>
-      <c r="C16" s="274"/>
-      <c r="D16" s="275">
+      <c r="C16" s="215"/>
+      <c r="D16" s="216">
         <f t="shared" si="22"/>
         <v>34088</v>
       </c>
-      <c r="E16" s="276">
+      <c r="E16" s="217">
         <f t="shared" si="54"/>
-        <v>0.81277869044825157</v>
-      </c>
-      <c r="F16" s="275">
+        <v>0.79819877962919505</v>
+      </c>
+      <c r="F16" s="216">
         <f t="shared" si="24"/>
-        <v>27706</v>
-      </c>
-      <c r="G16" s="276">
+        <v>27209</v>
+      </c>
+      <c r="G16" s="217">
         <f t="shared" si="55"/>
-        <v>0.18722130955174843</v>
-      </c>
-      <c r="H16" s="277">
-        <f t="shared" si="26"/>
-        <v>6382</v>
-      </c>
-      <c r="I16" s="278">
+        <v>0.20180122037080497</v>
+      </c>
+      <c r="H16" s="270">
+        <f t="shared" si="49"/>
+        <v>6879</v>
+      </c>
+      <c r="I16" s="219">
         <f t="shared" si="56"/>
         <v>7.7811324752370362E-2</v>
       </c>
-      <c r="J16" s="276">
+      <c r="J16" s="217">
         <f t="shared" si="57"/>
         <v>0.15379522220456593</v>
       </c>
-      <c r="K16" s="276">
+      <c r="K16" s="217">
         <f t="shared" si="58"/>
         <v>0.16623885436368549</v>
       </c>
-      <c r="L16" s="279">
+      <c r="L16" s="220">
         <f t="shared" si="59"/>
         <v>0.63803697229726153</v>
       </c>
-      <c r="M16" s="277">
+      <c r="M16" s="218">
         <f t="shared" si="60"/>
         <v>2541.8625456856826</v>
       </c>
-      <c r="N16" s="277">
+      <c r="N16" s="218">
         <f t="shared" si="61"/>
         <v>5024.0285237565549</v>
       </c>
-      <c r="O16" s="277">
+      <c r="O16" s="218">
         <f t="shared" si="62"/>
         <v>5430.5246554985142</v>
       </c>
-      <c r="P16" s="277">
+      <c r="P16" s="218">
         <f t="shared" si="63"/>
         <v>20842.753774034642</v>
       </c>
-      <c r="Q16" s="273">
+      <c r="Q16" s="214">
         <f t="shared" si="50"/>
         <v>46032</v>
       </c>
-      <c r="R16" s="280">
+      <c r="R16" s="221">
         <v>34088</v>
       </c>
-      <c r="S16" s="281">
-        <v>0</v>
-      </c>
-      <c r="T16" s="281">
+      <c r="S16" s="222">
+        <v>0</v>
+      </c>
+      <c r="T16" s="222">
         <v>32667</v>
       </c>
-      <c r="U16" s="281">
-        <v>0</v>
-      </c>
-      <c r="V16" s="282">
+      <c r="U16" s="222">
+        <v>0</v>
+      </c>
+      <c r="V16" s="223">
         <v>6265</v>
       </c>
-      <c r="W16" s="283">
+      <c r="W16" s="224">
         <v>0.875</v>
       </c>
-      <c r="X16" s="282">
+      <c r="X16" s="223">
         <v>2109</v>
       </c>
-      <c r="Y16" s="283">
+      <c r="Y16" s="224">
         <v>0.88541666666666663</v>
       </c>
-      <c r="Z16" s="282">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="283">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="273">
+      <c r="Z16" s="223">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="224">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="214">
         <f t="shared" si="51"/>
         <v>46032</v>
       </c>
-      <c r="AC16" s="284">
+      <c r="AC16" s="225">
         <f t="shared" si="64"/>
         <v>1</v>
       </c>
-      <c r="AD16" s="285">
+      <c r="AD16" s="226">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="286">
+      <c r="AE16" s="227">
         <v>2938</v>
       </c>
-      <c r="AF16" s="287">
+      <c r="AF16" s="228">
+        <f t="shared" si="36"/>
+        <v>2938</v>
+      </c>
+      <c r="AG16" s="218">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="229">
+        <v>1633</v>
+      </c>
+      <c r="AI16" s="230">
+        <v>0.7368055555555556</v>
+      </c>
+      <c r="AJ16" s="229">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="231">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="214">
         <f t="shared" si="37"/>
-        <v>2938</v>
-      </c>
-      <c r="AG16" s="277">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="288">
-        <v>1633</v>
-      </c>
-      <c r="AI16" s="289">
-        <v>0.7368055555555556</v>
-      </c>
-      <c r="AJ16" s="288">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="290">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="273">
-        <f t="shared" si="38"/>
         <v>46032</v>
       </c>
-      <c r="AM16" s="291">
+      <c r="AM16" s="232">
         <f t="shared" si="66"/>
         <v>0.36697089719304288</v>
       </c>
-      <c r="AN16" s="284">
+      <c r="AN16" s="225">
         <f t="shared" si="67"/>
         <v>0.63302910280695712</v>
       </c>
-      <c r="AO16" s="292">
+      <c r="AO16" s="233">
         <v>5807</v>
       </c>
-      <c r="AP16" s="293">
-        <f t="shared" si="41"/>
+      <c r="AP16" s="234">
+        <f t="shared" si="40"/>
         <v>2131</v>
       </c>
-      <c r="AQ16" s="294">
+      <c r="AQ16" s="235">
         <v>3676</v>
       </c>
-      <c r="AR16" s="288">
+      <c r="AR16" s="229">
         <v>1702</v>
       </c>
-      <c r="AS16" s="295">
+      <c r="AS16" s="236">
         <v>0.72916666666666663</v>
       </c>
-      <c r="AT16" s="288">
+      <c r="AT16" s="229">
         <v>180</v>
       </c>
-      <c r="AU16" s="296">
+      <c r="AU16" s="237">
         <v>0.875</v>
       </c>
-      <c r="AV16" s="273">
+      <c r="AV16" s="214">
         <f t="shared" si="52"/>
         <v>46032</v>
       </c>
-      <c r="AW16" s="297">
+      <c r="AW16" s="238">
         <f t="shared" si="68"/>
-        <v>0.45022348638764731</v>
-      </c>
-      <c r="AX16" s="297">
+        <v>0.34924827305973183</v>
+      </c>
+      <c r="AX16" s="238">
         <f t="shared" si="69"/>
-        <v>0.54977651361235269</v>
-      </c>
-      <c r="AY16" s="298">
-        <f t="shared" si="44"/>
+        <v>0.65075172694026817</v>
+      </c>
+      <c r="AY16" s="239">
+        <f t="shared" si="43"/>
         <v>4922</v>
       </c>
-      <c r="AZ16" s="299">
+      <c r="AZ16" s="240">
         <v>4922</v>
       </c>
-      <c r="BA16" s="300">
+      <c r="BA16" s="241">
         <f t="shared" si="76"/>
-        <v>2216</v>
-      </c>
-      <c r="BB16" s="298">
-        <v>2706</v>
-      </c>
-      <c r="BC16" s="299">
+        <v>1719</v>
+      </c>
+      <c r="BB16" s="239">
+        <f>2706+497</f>
+        <v>3203</v>
+      </c>
+      <c r="BC16" s="240">
         <v>1670</v>
       </c>
-      <c r="BD16" s="301">
+      <c r="BD16" s="242">
         <v>0.91666666666666663</v>
       </c>
-      <c r="BE16" s="302">
-        <v>0</v>
-      </c>
-      <c r="BF16" s="301">
-        <v>0</v>
-      </c>
-      <c r="BG16" s="302">
+      <c r="BE16" s="243">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="242">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="243">
         <v>161</v>
       </c>
-      <c r="BH16" s="301">
+      <c r="BH16" s="242">
         <v>0.91666666666666663</v>
       </c>
-      <c r="BI16" s="273">
+      <c r="BI16" s="214">
         <f t="shared" si="53"/>
         <v>46032</v>
       </c>
-      <c r="BJ16" s="303">
+      <c r="BJ16" s="244">
         <f t="shared" si="70"/>
         <v>0.60997883026856503</v>
       </c>
-      <c r="BK16" s="284">
+      <c r="BK16" s="225">
         <f t="shared" si="71"/>
         <v>0.39002116973143497</v>
       </c>
-      <c r="BL16" s="304">
+      <c r="BL16" s="245">
         <f t="shared" si="72"/>
         <v>24091</v>
       </c>
-      <c r="BM16" s="277">
+      <c r="BM16" s="218">
         <v>14695</v>
       </c>
-      <c r="BN16" s="277">
+      <c r="BN16" s="218">
         <v>9396</v>
       </c>
-      <c r="BO16" s="305">
+      <c r="BO16" s="246">
         <v>2581</v>
       </c>
-      <c r="BP16" s="289">
+      <c r="BP16" s="230">
         <v>0.42638888888888887</v>
       </c>
-      <c r="BQ16" s="306">
+      <c r="BQ16" s="247">
         <v>1739</v>
       </c>
-      <c r="BR16" s="289">
+      <c r="BR16" s="230">
         <v>0.36805555555555558</v>
       </c>
+      <c r="BU16" s="267"/>
     </row>
-    <row r="17" spans="1:70" s="271" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="244"/>
-      <c r="B17" s="245">
-        <f t="shared" si="49"/>
+    <row r="17" spans="1:73" s="212" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="185"/>
+      <c r="B17" s="186">
+        <f t="shared" si="48"/>
         <v>46033</v>
       </c>
-      <c r="C17" s="325"/>
-      <c r="D17" s="247">
+      <c r="C17" s="266"/>
+      <c r="D17" s="188">
         <f t="shared" si="22"/>
         <v>28084</v>
       </c>
-      <c r="E17" s="248">
+      <c r="E17" s="189">
         <f t="shared" si="54"/>
-        <v>0.77588662583677537</v>
-      </c>
-      <c r="F17" s="247">
+        <v>0.75818971656459189</v>
+      </c>
+      <c r="F17" s="188">
         <f t="shared" si="24"/>
-        <v>21790</v>
-      </c>
-      <c r="G17" s="248">
+        <v>21293</v>
+      </c>
+      <c r="G17" s="189">
         <f t="shared" si="55"/>
-        <v>0.2241133741632246</v>
-      </c>
-      <c r="H17" s="154">
-        <f t="shared" si="26"/>
-        <v>6294</v>
-      </c>
-      <c r="I17" s="249">
+        <v>0.24181028343540806</v>
+      </c>
+      <c r="H17" s="268">
+        <f t="shared" si="49"/>
+        <v>6791</v>
+      </c>
+      <c r="I17" s="190">
         <f t="shared" si="56"/>
         <v>6.5586647029946002E-2</v>
       </c>
-      <c r="J17" s="248">
+      <c r="J17" s="189">
         <f t="shared" si="57"/>
         <v>0.16920307641957127</v>
       </c>
-      <c r="K17" s="248">
+      <c r="K17" s="189">
         <f t="shared" si="58"/>
         <v>0.18501982057166702</v>
       </c>
-      <c r="L17" s="250">
+      <c r="L17" s="191">
         <f t="shared" si="59"/>
         <v>0.62009491081656032</v>
       </c>
@@ -10479,7 +10500,7 @@
         <f t="shared" si="63"/>
         <v>16639.626836851581</v>
       </c>
-      <c r="Q17" s="245">
+      <c r="Q17" s="186">
         <f t="shared" si="50"/>
         <v>46033</v>
       </c>
@@ -10513,131 +10534,132 @@
       <c r="AA17" s="141">
         <v>0</v>
       </c>
-      <c r="AB17" s="245">
+      <c r="AB17" s="186">
         <f t="shared" si="51"/>
         <v>46033</v>
       </c>
-      <c r="AC17" s="251">
+      <c r="AC17" s="192">
         <f t="shared" si="64"/>
         <v>1</v>
       </c>
-      <c r="AD17" s="252">
+      <c r="AD17" s="193">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AE17" s="253">
+      <c r="AE17" s="194">
         <v>2004</v>
       </c>
-      <c r="AF17" s="254">
-        <f t="shared" si="37"/>
+      <c r="AF17" s="195">
+        <f t="shared" si="36"/>
         <v>2004</v>
       </c>
       <c r="AG17" s="154">
         <v>0</v>
       </c>
-      <c r="AH17" s="255">
+      <c r="AH17" s="196">
         <v>1436</v>
       </c>
       <c r="AI17" s="156">
         <v>0.92291666666666672</v>
       </c>
-      <c r="AJ17" s="255">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="256">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="245">
-        <f t="shared" si="38"/>
+      <c r="AJ17" s="196">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="197">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="186">
+        <f t="shared" si="37"/>
         <v>46033</v>
       </c>
-      <c r="AM17" s="257">
+      <c r="AM17" s="198">
         <f t="shared" si="66"/>
         <v>0.29574468085106381</v>
       </c>
-      <c r="AN17" s="251">
+      <c r="AN17" s="192">
         <f t="shared" si="67"/>
         <v>0.70425531914893613</v>
       </c>
-      <c r="AO17" s="258">
+      <c r="AO17" s="199">
         <v>5170</v>
       </c>
-      <c r="AP17" s="259">
-        <f t="shared" si="41"/>
+      <c r="AP17" s="200">
+        <f t="shared" si="40"/>
         <v>1529</v>
       </c>
-      <c r="AQ17" s="260">
+      <c r="AQ17" s="201">
         <v>3641</v>
       </c>
-      <c r="AR17" s="255">
+      <c r="AR17" s="196">
         <v>1706</v>
       </c>
-      <c r="AS17" s="261">
+      <c r="AS17" s="202">
         <v>0.93194444444444446</v>
       </c>
-      <c r="AT17" s="255">
+      <c r="AT17" s="196">
         <v>173</v>
       </c>
-      <c r="AU17" s="262">
+      <c r="AU17" s="203">
         <v>0.92708333333333337</v>
       </c>
-      <c r="AV17" s="245">
+      <c r="AV17" s="186">
         <f t="shared" si="52"/>
         <v>46033</v>
       </c>
-      <c r="AW17" s="263">
+      <c r="AW17" s="204">
         <f t="shared" si="68"/>
-        <v>0.40166892196662157</v>
-      </c>
-      <c r="AX17" s="263">
+        <v>0.28958051420838971</v>
+      </c>
+      <c r="AX17" s="204">
         <f t="shared" si="69"/>
-        <v>0.59833107803337848</v>
-      </c>
-      <c r="AY17" s="264">
-        <f t="shared" si="44"/>
+        <v>0.71041948579161029</v>
+      </c>
+      <c r="AY17" s="205">
+        <f t="shared" si="43"/>
         <v>4434</v>
       </c>
-      <c r="AZ17" s="265">
+      <c r="AZ17" s="206">
         <v>4434</v>
       </c>
-      <c r="BA17" s="266">
+      <c r="BA17" s="207">
         <f t="shared" si="76"/>
-        <v>1781</v>
-      </c>
-      <c r="BB17" s="264">
-        <v>2653</v>
-      </c>
-      <c r="BC17" s="265">
+        <v>1284</v>
+      </c>
+      <c r="BB17" s="205">
+        <f>2653+497</f>
+        <v>3150</v>
+      </c>
+      <c r="BC17" s="206">
         <v>1625</v>
       </c>
-      <c r="BD17" s="267">
+      <c r="BD17" s="208">
         <v>0.41666666666666669</v>
       </c>
-      <c r="BE17" s="268">
-        <v>0</v>
-      </c>
-      <c r="BF17" s="267">
-        <v>0</v>
-      </c>
-      <c r="BG17" s="268">
+      <c r="BE17" s="209">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="208">
+        <v>0</v>
+      </c>
+      <c r="BG17" s="209">
         <v>160</v>
       </c>
-      <c r="BH17" s="267">
+      <c r="BH17" s="208">
         <v>0.89583333333333337</v>
       </c>
-      <c r="BI17" s="245">
+      <c r="BI17" s="186">
         <f t="shared" si="53"/>
         <v>46033</v>
       </c>
-      <c r="BJ17" s="269">
+      <c r="BJ17" s="210">
         <f t="shared" si="70"/>
         <v>0.61033408982952442</v>
       </c>
-      <c r="BK17" s="251">
+      <c r="BK17" s="192">
         <f t="shared" si="71"/>
         <v>0.38966591017047553</v>
       </c>
-      <c r="BL17" s="270">
+      <c r="BL17" s="211">
         <f t="shared" si="72"/>
         <v>18947</v>
       </c>
@@ -10659,10 +10681,11 @@
       <c r="BR17" s="156">
         <v>0.41875000000000001</v>
       </c>
+      <c r="BU17" s="267"/>
     </row>
-    <row r="18" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46034</v>
       </c>
       <c r="C18" s="163"/>
@@ -10672,19 +10695,19 @@
       </c>
       <c r="E18" s="158">
         <f t="shared" si="54"/>
-        <v>0.87286278625954206</v>
+        <v>0.86337805343511453</v>
       </c>
       <c r="F18" s="87">
         <f t="shared" si="24"/>
-        <v>45738.01</v>
+        <v>45241.01</v>
       </c>
       <c r="G18" s="158">
         <f t="shared" si="55"/>
-        <v>0.127137213740458</v>
-      </c>
-      <c r="H18" s="145">
-        <f t="shared" si="26"/>
-        <v>6661.99</v>
+        <v>0.13662194656488549</v>
+      </c>
+      <c r="H18" s="269">
+        <f t="shared" si="49"/>
+        <v>7158.99</v>
       </c>
       <c r="I18" s="159">
         <f t="shared" si="56"/>
@@ -10768,7 +10791,7 @@
         <v>6905</v>
       </c>
       <c r="AF18" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6905</v>
       </c>
       <c r="AG18" s="146">
@@ -10787,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46034</v>
       </c>
       <c r="AM18" s="77">
@@ -10802,7 +10825,7 @@
         <v>9328.5</v>
       </c>
       <c r="AP18" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5420.7</v>
       </c>
       <c r="AQ18" s="150">
@@ -10826,14 +10849,14 @@
       </c>
       <c r="AW18" s="110">
         <f t="shared" si="68"/>
-        <v>0.67419530372035241</v>
+        <v>0.6154030874785591</v>
       </c>
       <c r="AX18" s="110">
         <f t="shared" si="69"/>
-        <v>0.32580469627964748</v>
+        <v>0.38459691252144085</v>
       </c>
       <c r="AY18" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8453.5</v>
       </c>
       <c r="AZ18" s="112">
@@ -10841,10 +10864,11 @@
       </c>
       <c r="BA18" s="120">
         <f t="shared" si="76"/>
-        <v>5699.3099999999995</v>
+        <v>5202.3099999999995</v>
       </c>
       <c r="BB18" s="113">
-        <v>2754.19</v>
+        <f>2754.19+497</f>
+        <v>3251.19</v>
       </c>
       <c r="BC18" s="112">
         <v>3395.8</v>
@@ -10898,10 +10922,11 @@
       <c r="BR18" s="156">
         <v>0.78611111111111109</v>
       </c>
+      <c r="BU18" s="267"/>
     </row>
-    <row r="19" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46035</v>
       </c>
       <c r="C19" s="163"/>
@@ -10911,19 +10936,19 @@
       </c>
       <c r="E19" s="158">
         <f t="shared" si="54"/>
-        <v>0.89111817486822509</v>
+        <v>0.88111938196595985</v>
       </c>
       <c r="F19" s="87">
         <f t="shared" si="24"/>
-        <v>44293.919999999998</v>
+        <v>43796.92</v>
       </c>
       <c r="G19" s="158">
         <f t="shared" si="55"/>
-        <v>0.10888182513177483</v>
-      </c>
-      <c r="H19" s="145">
-        <f t="shared" si="26"/>
-        <v>5412.08</v>
+        <v>0.11888061803404015</v>
+      </c>
+      <c r="H19" s="269">
+        <f t="shared" si="49"/>
+        <v>5909.08</v>
       </c>
       <c r="I19" s="159">
         <f t="shared" si="56"/>
@@ -11007,7 +11032,7 @@
         <v>9525</v>
       </c>
       <c r="AF19" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>9525</v>
       </c>
       <c r="AG19" s="146">
@@ -11026,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="AL19" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46035</v>
       </c>
       <c r="AM19" s="77">
@@ -11041,7 +11066,7 @@
         <v>10961</v>
       </c>
       <c r="AP19" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>7033.8</v>
       </c>
       <c r="AQ19" s="150">
@@ -11065,14 +11090,14 @@
       </c>
       <c r="AW19" s="110">
         <f t="shared" ref="AW19" si="79">BA19/AZ19</f>
-        <v>0.69733387688544635</v>
+        <v>0.5960293518141051</v>
       </c>
       <c r="AX19" s="110">
         <f t="shared" ref="AX19" si="80">BB19/AZ19</f>
-        <v>0.30266612311455365</v>
+        <v>0.40397064818589484</v>
       </c>
       <c r="AY19" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>4906</v>
       </c>
       <c r="AZ19" s="112">
@@ -11080,10 +11105,11 @@
       </c>
       <c r="BA19" s="120">
         <f t="shared" si="76"/>
-        <v>3421.12</v>
+        <v>2924.12</v>
       </c>
       <c r="BB19" s="113">
-        <v>1484.88</v>
+        <f>1484.88+497</f>
+        <v>1981.88</v>
       </c>
       <c r="BC19" s="183">
         <v>4060.52</v>
@@ -11137,10 +11163,11 @@
       <c r="BR19" s="156">
         <v>0.34305555555555556</v>
       </c>
+      <c r="BU19" s="267"/>
     </row>
-    <row r="20" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46036</v>
       </c>
       <c r="C20" s="163"/>
@@ -11150,19 +11177,19 @@
       </c>
       <c r="E20" s="158">
         <f t="shared" si="54"/>
-        <v>0.87005457707762734</v>
+        <v>0.86011875012494754</v>
       </c>
       <c r="F20" s="87">
         <f t="shared" si="24"/>
-        <v>43521</v>
+        <v>43024</v>
       </c>
       <c r="G20" s="158">
         <f t="shared" si="55"/>
-        <v>0.1299454229223726</v>
-      </c>
-      <c r="H20" s="145">
-        <f t="shared" si="26"/>
-        <v>6500</v>
+        <v>0.13988124987505249</v>
+      </c>
+      <c r="H20" s="269">
+        <f t="shared" si="49"/>
+        <v>6997</v>
       </c>
       <c r="I20" s="159">
         <f t="shared" si="56"/>
@@ -11246,7 +11273,7 @@
         <v>7250</v>
       </c>
       <c r="AF20" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7250</v>
       </c>
       <c r="AG20" s="146">
@@ -11265,7 +11292,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46036</v>
       </c>
       <c r="AM20" s="77">
@@ -11280,7 +11307,7 @@
         <v>9280</v>
       </c>
       <c r="AP20" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5470</v>
       </c>
       <c r="AQ20" s="150">
@@ -11304,14 +11331,14 @@
       </c>
       <c r="AW20" s="110">
         <f t="shared" si="68"/>
-        <v>0.61461318051575931</v>
+        <v>0.54340974212034387</v>
       </c>
       <c r="AX20" s="110">
         <f t="shared" si="69"/>
-        <v>0.38538681948424069</v>
+        <v>0.45659025787965618</v>
       </c>
       <c r="AY20" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>6980</v>
       </c>
       <c r="AZ20" s="112">
@@ -11319,10 +11346,11 @@
       </c>
       <c r="BA20" s="120">
         <f t="shared" ref="BA20" si="84">AZ20-BB20</f>
-        <v>4290</v>
+        <v>3793</v>
       </c>
       <c r="BB20" s="113">
-        <v>2690</v>
+        <f>2690+497</f>
+        <v>3187</v>
       </c>
       <c r="BC20" s="112">
         <v>3820</v>
@@ -11376,11 +11404,12 @@
       <c r="BR20" s="156">
         <v>0.3125</v>
       </c>
+      <c r="BU20" s="267"/>
     </row>
-    <row r="21" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
       <c r="B21" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46037</v>
       </c>
       <c r="C21" s="163"/>
@@ -11390,19 +11419,19 @@
       </c>
       <c r="E21" s="158">
         <f t="shared" si="54"/>
-        <v>0.87401869158878509</v>
+        <v>0.86472897196261678</v>
       </c>
       <c r="F21" s="87">
         <f t="shared" si="24"/>
-        <v>46760</v>
+        <v>46263</v>
       </c>
       <c r="G21" s="158">
         <f t="shared" si="55"/>
-        <v>0.12598130841121497</v>
-      </c>
-      <c r="H21" s="145">
-        <f t="shared" si="26"/>
-        <v>6740</v>
+        <v>0.13527102803738317</v>
+      </c>
+      <c r="H21" s="269">
+        <f t="shared" si="49"/>
+        <v>7237</v>
       </c>
       <c r="I21" s="159">
         <f t="shared" si="56"/>
@@ -11486,7 +11515,7 @@
         <v>7370</v>
       </c>
       <c r="AF21" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7370</v>
       </c>
       <c r="AG21" s="146">
@@ -11505,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="AL21" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46037</v>
       </c>
       <c r="AM21" s="77">
@@ -11520,7 +11549,7 @@
         <v>8970</v>
       </c>
       <c r="AP21" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4960</v>
       </c>
       <c r="AQ21" s="150">
@@ -11544,14 +11573,14 @@
       </c>
       <c r="AW21" s="110">
         <f t="shared" si="68"/>
-        <v>0.66379310344827591</v>
+        <v>0.60258620689655173</v>
       </c>
       <c r="AX21" s="110">
         <f t="shared" si="69"/>
-        <v>0.33620689655172414</v>
+        <v>0.39741379310344827</v>
       </c>
       <c r="AY21" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8120</v>
       </c>
       <c r="AZ21" s="112">
@@ -11559,10 +11588,11 @@
       </c>
       <c r="BA21" s="120">
         <f t="shared" si="76"/>
-        <v>5390</v>
+        <v>4893</v>
       </c>
       <c r="BB21" s="113">
-        <v>2730</v>
+        <f>2730+497</f>
+        <v>3227</v>
       </c>
       <c r="BC21" s="112">
         <v>3980</v>
@@ -11616,11 +11646,12 @@
       <c r="BR21" s="156">
         <v>0.75</v>
       </c>
+      <c r="BU21" s="267"/>
     </row>
-    <row r="22" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
       <c r="B22" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46038</v>
       </c>
       <c r="C22" s="163"/>
@@ -11630,19 +11661,19 @@
       </c>
       <c r="E22" s="158">
         <f t="shared" si="54"/>
-        <v>0.87196531791907517</v>
+        <v>0.86238921001926783</v>
       </c>
       <c r="F22" s="87">
         <f t="shared" si="24"/>
-        <v>45255</v>
+        <v>44758</v>
       </c>
       <c r="G22" s="158">
         <f t="shared" si="55"/>
-        <v>0.12803468208092486</v>
-      </c>
-      <c r="H22" s="145">
-        <f t="shared" si="26"/>
-        <v>6645</v>
+        <v>0.13761078998073217</v>
+      </c>
+      <c r="H22" s="269">
+        <f t="shared" si="49"/>
+        <v>7142</v>
       </c>
       <c r="I22" s="159">
         <f t="shared" si="56"/>
@@ -11726,7 +11757,7 @@
         <v>6980</v>
       </c>
       <c r="AF22" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6980</v>
       </c>
       <c r="AG22" s="146">
@@ -11745,7 +11776,7 @@
         <v>0</v>
       </c>
       <c r="AL22" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46038</v>
       </c>
       <c r="AM22" s="77">
@@ -11760,7 +11791,7 @@
         <v>9270</v>
       </c>
       <c r="AP22" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5320</v>
       </c>
       <c r="AQ22" s="150">
@@ -11784,14 +11815,14 @@
       </c>
       <c r="AW22" s="110">
         <f t="shared" si="68"/>
-        <v>0.66851168511685122</v>
+        <v>0.607380073800738</v>
       </c>
       <c r="AX22" s="110">
         <f t="shared" si="69"/>
-        <v>0.33148831488314884</v>
+        <v>0.392619926199262</v>
       </c>
       <c r="AY22" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8130</v>
       </c>
       <c r="AZ22" s="112">
@@ -11799,10 +11830,11 @@
       </c>
       <c r="BA22" s="120">
         <f t="shared" si="76"/>
-        <v>5435</v>
+        <v>4938</v>
       </c>
       <c r="BB22" s="113">
-        <v>2695</v>
+        <f>2695+497</f>
+        <v>3192</v>
       </c>
       <c r="BC22" s="112">
         <v>3790</v>
@@ -11856,287 +11888,290 @@
       <c r="BR22" s="156">
         <v>0.875</v>
       </c>
+      <c r="BU22" s="267"/>
     </row>
-    <row r="23" spans="1:70" s="307" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="272"/>
-      <c r="B23" s="273">
-        <f t="shared" si="49"/>
+    <row r="23" spans="1:73" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="213"/>
+      <c r="B23" s="214">
+        <f t="shared" si="48"/>
         <v>46039</v>
       </c>
-      <c r="C23" s="274"/>
-      <c r="D23" s="275">
+      <c r="C23" s="215"/>
+      <c r="D23" s="216">
         <f t="shared" si="22"/>
         <v>33744</v>
       </c>
-      <c r="E23" s="276">
+      <c r="E23" s="217">
         <f t="shared" si="54"/>
-        <v>0.79821597913703179</v>
-      </c>
-      <c r="F23" s="275">
+        <v>0.78348743480322425</v>
+      </c>
+      <c r="F23" s="216">
         <f t="shared" si="24"/>
-        <v>26935</v>
-      </c>
-      <c r="G23" s="276">
+        <v>26438</v>
+      </c>
+      <c r="G23" s="217">
         <f t="shared" si="55"/>
-        <v>0.20178402086296823</v>
-      </c>
-      <c r="H23" s="277">
-        <f t="shared" si="26"/>
-        <v>6809</v>
-      </c>
-      <c r="I23" s="278">
+        <v>0.21651256519677572</v>
+      </c>
+      <c r="H23" s="270">
+        <f t="shared" si="49"/>
+        <v>7306</v>
+      </c>
+      <c r="I23" s="219">
         <f t="shared" si="56"/>
         <v>8.0408858603066444E-2</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="217">
         <f t="shared" si="57"/>
         <v>0.12624819813916918</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="217">
         <f t="shared" si="58"/>
         <v>0.16971564923444024</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="220">
         <f t="shared" si="59"/>
         <v>0.65912724413576207</v>
       </c>
-      <c r="M23" s="277">
+      <c r="M23" s="218">
         <f t="shared" si="60"/>
         <v>2593.8289608177174</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="218">
         <f t="shared" si="61"/>
         <v>4072.5143755733193</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="218">
         <f t="shared" si="62"/>
         <v>5474.6874130045735</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="218">
         <f t="shared" si="63"/>
         <v>21262.126641331412</v>
       </c>
-      <c r="Q23" s="273">
+      <c r="Q23" s="214">
         <f t="shared" si="50"/>
         <v>46039</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="221">
         <v>33744</v>
       </c>
-      <c r="S23" s="281">
-        <v>0</v>
-      </c>
-      <c r="T23" s="281">
+      <c r="S23" s="222">
+        <v>0</v>
+      </c>
+      <c r="T23" s="222">
         <v>32258</v>
       </c>
-      <c r="U23" s="281">
-        <v>0</v>
-      </c>
-      <c r="V23" s="282">
+      <c r="U23" s="222">
+        <v>0</v>
+      </c>
+      <c r="V23" s="223">
         <v>6644</v>
       </c>
-      <c r="W23" s="283">
+      <c r="W23" s="224">
         <v>0.48958333333333331</v>
       </c>
-      <c r="X23" s="282">
+      <c r="X23" s="223">
         <v>2053</v>
       </c>
-      <c r="Y23" s="283">
+      <c r="Y23" s="224">
         <v>0.88541666666666663</v>
       </c>
-      <c r="Z23" s="282">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="283">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="273">
+      <c r="Z23" s="223">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="224">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="214">
         <f t="shared" si="51"/>
         <v>46039</v>
       </c>
-      <c r="AC23" s="284">
+      <c r="AC23" s="225">
         <f t="shared" si="64"/>
         <v>1</v>
       </c>
-      <c r="AD23" s="285">
+      <c r="AD23" s="226">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="286">
+      <c r="AE23" s="227">
         <v>3068</v>
       </c>
-      <c r="AF23" s="287">
+      <c r="AF23" s="228">
+        <f t="shared" si="36"/>
+        <v>3068</v>
+      </c>
+      <c r="AG23" s="218">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="229">
+        <v>1840</v>
+      </c>
+      <c r="AI23" s="230">
+        <v>0.93472222222222223</v>
+      </c>
+      <c r="AJ23" s="229">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="231">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="214">
         <f t="shared" si="37"/>
-        <v>3068</v>
-      </c>
-      <c r="AG23" s="277">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="288">
-        <v>1840</v>
-      </c>
-      <c r="AI23" s="289">
-        <v>0.93472222222222223</v>
-      </c>
-      <c r="AJ23" s="288">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="290">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="273">
-        <f t="shared" si="38"/>
         <v>46039</v>
       </c>
-      <c r="AM23" s="291">
+      <c r="AM23" s="232">
         <f t="shared" si="66"/>
         <v>0.19223583143035083</v>
       </c>
-      <c r="AN23" s="284">
+      <c r="AN23" s="225">
         <f t="shared" si="67"/>
         <v>0.80776416856964917</v>
       </c>
-      <c r="AO23" s="292">
+      <c r="AO23" s="233">
         <v>4817</v>
       </c>
-      <c r="AP23" s="293">
-        <f t="shared" si="41"/>
+      <c r="AP23" s="234">
+        <f t="shared" si="40"/>
         <v>926</v>
       </c>
-      <c r="AQ23" s="294">
+      <c r="AQ23" s="235">
         <v>3891</v>
       </c>
-      <c r="AR23" s="288">
+      <c r="AR23" s="229">
         <v>1709</v>
       </c>
-      <c r="AS23" s="295">
+      <c r="AS23" s="236">
         <v>0.95208333333333328</v>
       </c>
-      <c r="AT23" s="288">
+      <c r="AT23" s="229">
         <v>183</v>
       </c>
-      <c r="AU23" s="296">
+      <c r="AU23" s="237">
         <v>0.89583333333333337</v>
       </c>
-      <c r="AV23" s="273">
+      <c r="AV23" s="214">
         <f t="shared" si="52"/>
         <v>46039</v>
       </c>
-      <c r="AW23" s="297">
+      <c r="AW23" s="238">
         <f t="shared" si="68"/>
-        <v>0.43018941612966216</v>
-      </c>
-      <c r="AX23" s="297">
+        <v>0.33313805897285687</v>
+      </c>
+      <c r="AX23" s="238">
         <f t="shared" si="69"/>
-        <v>0.56981058387033778</v>
-      </c>
-      <c r="AY23" s="298">
-        <f t="shared" si="44"/>
+        <v>0.66686194102714313</v>
+      </c>
+      <c r="AY23" s="239">
+        <f t="shared" si="43"/>
         <v>5121</v>
       </c>
-      <c r="AZ23" s="299">
+      <c r="AZ23" s="240">
         <v>5121</v>
       </c>
-      <c r="BA23" s="300">
+      <c r="BA23" s="241">
         <f t="shared" si="76"/>
-        <v>2203</v>
-      </c>
-      <c r="BB23" s="298">
-        <v>2918</v>
-      </c>
-      <c r="BC23" s="299">
+        <v>1706</v>
+      </c>
+      <c r="BB23" s="239">
+        <f>2918+497</f>
+        <v>3415</v>
+      </c>
+      <c r="BC23" s="240">
         <v>1600</v>
       </c>
-      <c r="BD23" s="301">
+      <c r="BD23" s="242">
         <v>0.36458333333333331</v>
       </c>
-      <c r="BE23" s="302">
-        <v>0</v>
-      </c>
-      <c r="BF23" s="301">
-        <v>0</v>
-      </c>
-      <c r="BG23" s="302">
+      <c r="BE23" s="243">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="242">
+        <v>0</v>
+      </c>
+      <c r="BG23" s="243">
         <v>215</v>
       </c>
-      <c r="BH23" s="301">
+      <c r="BH23" s="242">
         <v>0.23958333333333334</v>
       </c>
-      <c r="BI23" s="273">
+      <c r="BI23" s="214">
         <f t="shared" si="53"/>
         <v>46039</v>
       </c>
-      <c r="BJ23" s="303">
+      <c r="BJ23" s="244">
         <f t="shared" si="70"/>
         <v>0.63374289236152526</v>
       </c>
-      <c r="BK23" s="284">
+      <c r="BK23" s="225">
         <f t="shared" si="71"/>
         <v>0.36625710763847469</v>
       </c>
-      <c r="BL23" s="304">
+      <c r="BL23" s="245">
         <f t="shared" si="72"/>
         <v>25149</v>
       </c>
-      <c r="BM23" s="277">
+      <c r="BM23" s="218">
         <v>15938</v>
       </c>
-      <c r="BN23" s="277">
+      <c r="BN23" s="218">
         <v>9211</v>
       </c>
-      <c r="BO23" s="305">
+      <c r="BO23" s="246">
         <v>2801</v>
       </c>
-      <c r="BP23" s="289">
+      <c r="BP23" s="230">
         <v>0.18472222222222223</v>
       </c>
-      <c r="BQ23" s="306">
+      <c r="BQ23" s="247">
         <v>1771</v>
       </c>
-      <c r="BR23" s="289">
+      <c r="BR23" s="230">
         <v>0.72916666666666663</v>
       </c>
+      <c r="BU23" s="267"/>
     </row>
-    <row r="24" spans="1:70" s="271" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="244"/>
-      <c r="B24" s="245">
-        <f t="shared" si="49"/>
+    <row r="24" spans="1:73" s="212" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="185"/>
+      <c r="B24" s="186">
+        <f t="shared" si="48"/>
         <v>46040</v>
       </c>
-      <c r="C24" s="325"/>
-      <c r="D24" s="247">
+      <c r="C24" s="266"/>
+      <c r="D24" s="188">
         <f t="shared" si="22"/>
         <v>31096</v>
       </c>
-      <c r="E24" s="248">
+      <c r="E24" s="189">
         <f t="shared" si="54"/>
-        <v>0.79320877283251867</v>
-      </c>
-      <c r="F24" s="247">
+        <v>0.77722600977617695</v>
+      </c>
+      <c r="F24" s="188">
         <f t="shared" si="24"/>
-        <v>24665.62</v>
-      </c>
-      <c r="G24" s="248">
+        <v>24168.62</v>
+      </c>
+      <c r="G24" s="189">
         <f t="shared" si="55"/>
-        <v>0.20679122716748136</v>
-      </c>
-      <c r="H24" s="154">
-        <f t="shared" si="26"/>
-        <v>6430.38</v>
-      </c>
-      <c r="I24" s="249">
+        <v>0.22277399022382299</v>
+      </c>
+      <c r="H24" s="268">
+        <f t="shared" si="49"/>
+        <v>6927.38</v>
+      </c>
+      <c r="I24" s="190">
         <f t="shared" si="56"/>
         <v>6.3765183974037035E-2</v>
       </c>
-      <c r="J24" s="248">
+      <c r="J24" s="189">
         <f t="shared" si="57"/>
         <v>0.15777908749254455</v>
       </c>
-      <c r="K24" s="248">
+      <c r="K24" s="189">
         <f t="shared" si="58"/>
         <v>0.1761701912645679</v>
       </c>
-      <c r="L24" s="250">
+      <c r="L24" s="191">
         <f t="shared" si="59"/>
         <v>0.64091605192829326</v>
       </c>
@@ -12156,7 +12191,7 @@
         <f t="shared" si="63"/>
         <v>19317.049576105775</v>
       </c>
-      <c r="Q24" s="245">
+      <c r="Q24" s="186">
         <f t="shared" si="50"/>
         <v>46040</v>
       </c>
@@ -12190,131 +12225,132 @@
       <c r="AA24" s="141">
         <v>0</v>
       </c>
-      <c r="AB24" s="245">
+      <c r="AB24" s="186">
         <f t="shared" si="51"/>
         <v>46040</v>
       </c>
-      <c r="AC24" s="251">
+      <c r="AC24" s="192">
         <f t="shared" si="64"/>
         <v>1</v>
       </c>
-      <c r="AD24" s="252">
+      <c r="AD24" s="193">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="AE24" s="253">
+      <c r="AE24" s="194">
         <v>2166</v>
       </c>
-      <c r="AF24" s="254">
-        <f t="shared" si="37"/>
+      <c r="AF24" s="195">
+        <f t="shared" si="36"/>
         <v>2166</v>
       </c>
       <c r="AG24" s="154">
         <v>0</v>
       </c>
-      <c r="AH24" s="255">
+      <c r="AH24" s="196">
         <v>1551.5</v>
       </c>
       <c r="AI24" s="156">
         <v>0.2013888888888889</v>
       </c>
-      <c r="AJ24" s="255">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="256">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="245">
-        <f t="shared" si="38"/>
+      <c r="AJ24" s="196">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="197">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="186">
+        <f t="shared" si="37"/>
         <v>46040</v>
       </c>
-      <c r="AM24" s="257">
+      <c r="AM24" s="198">
         <f t="shared" si="66"/>
         <v>0.3141953540442205</v>
       </c>
-      <c r="AN24" s="251">
+      <c r="AN24" s="192">
         <f t="shared" si="67"/>
         <v>0.6858046459557795</v>
       </c>
-      <c r="AO24" s="258">
+      <c r="AO24" s="199">
         <v>5359.5</v>
       </c>
-      <c r="AP24" s="259">
-        <f t="shared" si="41"/>
+      <c r="AP24" s="200">
+        <f t="shared" si="40"/>
         <v>1683.9299999999998</v>
       </c>
-      <c r="AQ24" s="260">
+      <c r="AQ24" s="201">
         <v>3675.57</v>
       </c>
-      <c r="AR24" s="255">
+      <c r="AR24" s="196">
         <v>1809.5</v>
       </c>
-      <c r="AS24" s="261">
+      <c r="AS24" s="202">
         <v>0.94305555555555554</v>
       </c>
-      <c r="AT24" s="255">
+      <c r="AT24" s="196">
         <v>172.25</v>
       </c>
-      <c r="AU24" s="262">
+      <c r="AU24" s="203">
         <v>0.9375</v>
       </c>
-      <c r="AV24" s="245">
+      <c r="AV24" s="186">
         <f t="shared" si="52"/>
         <v>46040</v>
       </c>
-      <c r="AW24" s="263">
+      <c r="AW24" s="204">
         <f t="shared" si="68"/>
-        <v>0.41035744863013701</v>
-      </c>
-      <c r="AX24" s="263">
+        <v>0.30397902397260274</v>
+      </c>
+      <c r="AX24" s="204">
         <f t="shared" si="69"/>
-        <v>0.58964255136986299</v>
-      </c>
-      <c r="AY24" s="264">
-        <f t="shared" si="44"/>
+        <v>0.69602097602739721</v>
+      </c>
+      <c r="AY24" s="205">
+        <f t="shared" si="43"/>
         <v>4672</v>
       </c>
-      <c r="AZ24" s="265">
+      <c r="AZ24" s="206">
         <v>4672</v>
       </c>
-      <c r="BA24" s="266">
+      <c r="BA24" s="207">
         <f t="shared" si="76"/>
-        <v>1917.19</v>
-      </c>
-      <c r="BB24" s="264">
-        <v>2754.81</v>
-      </c>
-      <c r="BC24" s="265">
+        <v>1420.19</v>
+      </c>
+      <c r="BB24" s="205">
+        <f>2754.81+497</f>
+        <v>3251.81</v>
+      </c>
+      <c r="BC24" s="206">
         <v>1540</v>
       </c>
-      <c r="BD24" s="267">
+      <c r="BD24" s="208">
         <v>0.76041666666666663</v>
       </c>
-      <c r="BE24" s="268">
-        <v>0</v>
-      </c>
-      <c r="BF24" s="267">
-        <v>0</v>
-      </c>
-      <c r="BG24" s="268">
+      <c r="BE24" s="209">
+        <v>0</v>
+      </c>
+      <c r="BF24" s="208">
+        <v>0</v>
+      </c>
+      <c r="BG24" s="209">
         <v>160.41999999999999</v>
       </c>
-      <c r="BH24" s="267">
+      <c r="BH24" s="208">
         <v>0.89583333333333337</v>
       </c>
-      <c r="BI24" s="245">
+      <c r="BI24" s="186">
         <f t="shared" si="53"/>
         <v>46040</v>
       </c>
-      <c r="BJ24" s="269">
+      <c r="BJ24" s="210">
         <f t="shared" si="70"/>
         <v>0.61209652526677838</v>
       </c>
-      <c r="BK24" s="251">
+      <c r="BK24" s="192">
         <f t="shared" si="71"/>
         <v>0.38790347473322168</v>
       </c>
-      <c r="BL24" s="270">
+      <c r="BL24" s="211">
         <f t="shared" si="72"/>
         <v>21770.879999999997</v>
       </c>
@@ -12336,11 +12372,12 @@
       <c r="BR24" s="156">
         <v>0.60624999999999996</v>
       </c>
+      <c r="BU24" s="267"/>
     </row>
-    <row r="25" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14"/>
       <c r="B25" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46041</v>
       </c>
       <c r="C25" s="163"/>
@@ -12350,19 +12387,19 @@
       </c>
       <c r="E25" s="158">
         <f t="shared" ref="E25:E36" si="85">F25/D25</f>
-        <v>0.86486048677762928</v>
+        <v>0.85479690600575065</v>
       </c>
       <c r="F25" s="87">
         <f t="shared" si="24"/>
-        <v>42712</v>
+        <v>42215</v>
       </c>
       <c r="G25" s="158">
         <f t="shared" ref="G25:G36" si="86">H25/D25</f>
-        <v>0.13513951322237072</v>
-      </c>
-      <c r="H25" s="145">
-        <f t="shared" si="26"/>
-        <v>6674</v>
+        <v>0.14520309399424938</v>
+      </c>
+      <c r="H25" s="269">
+        <f t="shared" si="49"/>
+        <v>7171</v>
       </c>
       <c r="I25" s="159">
         <f t="shared" ref="I25:I36" si="87">AE25/(AE25+AO25+BL25+AY25)</f>
@@ -12446,7 +12483,7 @@
         <v>6144</v>
       </c>
       <c r="AF25" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6144</v>
       </c>
       <c r="AG25" s="146">
@@ -12465,7 +12502,7 @@
         <v>0</v>
       </c>
       <c r="AL25" s="167">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46041</v>
       </c>
       <c r="AM25" s="77">
@@ -12480,7 +12517,7 @@
         <v>8715</v>
       </c>
       <c r="AP25" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4838</v>
       </c>
       <c r="AQ25" s="150">
@@ -12504,14 +12541,14 @@
       </c>
       <c r="AW25" s="168">
         <f t="shared" si="68"/>
-        <v>0.64364887246783031</v>
+        <v>0.58032870429354055</v>
       </c>
       <c r="AX25" s="168">
         <f t="shared" si="69"/>
-        <v>0.35635112753216969</v>
+        <v>0.41967129570645945</v>
       </c>
       <c r="AY25" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7849</v>
       </c>
       <c r="AZ25" s="112">
@@ -12519,10 +12556,11 @@
       </c>
       <c r="BA25" s="169">
         <f t="shared" si="76"/>
-        <v>5052</v>
+        <v>4555</v>
       </c>
       <c r="BB25" s="113">
-        <v>2797</v>
+        <f>2797+497</f>
+        <v>3294</v>
       </c>
       <c r="BC25" s="112">
         <v>3519</v>
@@ -12576,11 +12614,12 @@
       <c r="BR25" s="156">
         <v>0.7729166666666667</v>
       </c>
+      <c r="BU25" s="267"/>
     </row>
-    <row r="26" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14"/>
       <c r="B26" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46042</v>
       </c>
       <c r="C26" s="163"/>
@@ -12590,19 +12629,19 @@
       </c>
       <c r="E26" s="158">
         <f t="shared" si="85"/>
-        <v>0.87145593869731797</v>
+        <v>0.86193486590038315</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="24"/>
-        <v>45490</v>
+        <v>44993</v>
       </c>
       <c r="G26" s="158">
         <f t="shared" si="86"/>
-        <v>0.12854406130268201</v>
-      </c>
-      <c r="H26" s="145">
-        <f t="shared" si="26"/>
-        <v>6710</v>
+        <v>0.13806513409961685</v>
+      </c>
+      <c r="H26" s="269">
+        <f t="shared" si="49"/>
+        <v>7207</v>
       </c>
       <c r="I26" s="159">
         <f t="shared" si="87"/>
@@ -12686,7 +12725,7 @@
         <v>6293</v>
       </c>
       <c r="AF26" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6293</v>
       </c>
       <c r="AG26" s="146">
@@ -12705,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="AL26" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46042</v>
       </c>
       <c r="AM26" s="77">
@@ -12720,7 +12759,7 @@
         <v>8819</v>
       </c>
       <c r="AP26" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4927</v>
       </c>
       <c r="AQ26" s="150">
@@ -12744,14 +12783,14 @@
       </c>
       <c r="AW26" s="110">
         <f t="shared" ref="AW26:AW36" si="99">BA26/AZ26</f>
-        <v>0.64814583593457364</v>
+        <v>0.58609064802097643</v>
       </c>
       <c r="AX26" s="110">
         <f t="shared" ref="AX26:AX36" si="100">BB26/AZ26</f>
-        <v>0.35185416406542641</v>
+        <v>0.41390935197902362</v>
       </c>
       <c r="AY26" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>8009</v>
       </c>
       <c r="AZ26" s="112">
@@ -12759,10 +12798,11 @@
       </c>
       <c r="BA26" s="120">
         <f t="shared" ref="BA26:BA36" si="101">AZ26-BB26</f>
-        <v>5191</v>
+        <v>4694</v>
       </c>
       <c r="BB26" s="113">
-        <v>2818</v>
+        <f>2818+497</f>
+        <v>3315</v>
       </c>
       <c r="BC26" s="112">
         <v>3769</v>
@@ -12816,11 +12856,12 @@
       <c r="BR26" s="156">
         <v>0.79374999999999996</v>
       </c>
+      <c r="BU26" s="267"/>
     </row>
-    <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
       <c r="B27" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46043</v>
       </c>
       <c r="C27" s="163"/>
@@ -12830,19 +12871,19 @@
       </c>
       <c r="E27" s="158">
         <f t="shared" si="85"/>
-        <v>0.86584425597532766</v>
+        <v>0.85576025646228138</v>
       </c>
       <c r="F27" s="87">
         <f t="shared" si="24"/>
-        <v>42674</v>
+        <v>42177</v>
       </c>
       <c r="G27" s="158">
         <f t="shared" si="86"/>
-        <v>0.13415574402467231</v>
-      </c>
-      <c r="H27" s="145">
-        <f t="shared" si="26"/>
-        <v>6612</v>
+        <v>0.14423974353771862</v>
+      </c>
+      <c r="H27" s="269">
+        <f t="shared" si="49"/>
+        <v>7109</v>
       </c>
       <c r="I27" s="159">
         <f t="shared" si="87"/>
@@ -12926,7 +12967,7 @@
         <v>6135</v>
       </c>
       <c r="AF27" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6135</v>
       </c>
       <c r="AG27" s="146">
@@ -12945,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="AL27" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46043</v>
       </c>
       <c r="AM27" s="77">
@@ -12960,7 +13001,7 @@
         <v>8661</v>
       </c>
       <c r="AP27" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4747</v>
       </c>
       <c r="AQ27" s="150">
@@ -12984,14 +13025,14 @@
       </c>
       <c r="AW27" s="110">
         <f t="shared" si="99"/>
-        <v>0.64924596983879357</v>
+        <v>0.58463338533541342</v>
       </c>
       <c r="AX27" s="110">
         <f t="shared" si="100"/>
-        <v>0.35075403016120643</v>
+        <v>0.41536661466458658</v>
       </c>
       <c r="AY27" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7692</v>
       </c>
       <c r="AZ27" s="112">
@@ -12999,10 +13040,11 @@
       </c>
       <c r="BA27" s="120">
         <f t="shared" si="101"/>
-        <v>4994</v>
+        <v>4497</v>
       </c>
       <c r="BB27" s="113">
-        <v>2698</v>
+        <f>2698+497</f>
+        <v>3195</v>
       </c>
       <c r="BC27" s="112">
         <v>3231</v>
@@ -13056,11 +13098,12 @@
       <c r="BR27" s="156">
         <v>0.76736111111111116</v>
       </c>
+      <c r="BU27" s="267"/>
     </row>
-    <row r="28" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
       <c r="B28" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46044</v>
       </c>
       <c r="C28" s="163"/>
@@ -13070,19 +13113,19 @@
       </c>
       <c r="E28" s="158">
         <f t="shared" si="85"/>
-        <v>0.86782268269534957</v>
+        <v>0.85799588737741217</v>
       </c>
       <c r="F28" s="87">
         <f t="shared" si="24"/>
-        <v>43891</v>
+        <v>43394</v>
       </c>
       <c r="G28" s="158">
         <f t="shared" si="86"/>
-        <v>0.13217731730465043</v>
-      </c>
-      <c r="H28" s="145">
-        <f t="shared" si="26"/>
-        <v>6685</v>
+        <v>0.1420041126225878</v>
+      </c>
+      <c r="H28" s="269">
+        <f t="shared" si="49"/>
+        <v>7182</v>
       </c>
       <c r="I28" s="159">
         <f t="shared" si="87"/>
@@ -13166,7 +13209,7 @@
         <v>6261</v>
       </c>
       <c r="AF28" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6261</v>
       </c>
       <c r="AG28" s="146">
@@ -13185,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="AL28" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46044</v>
       </c>
       <c r="AM28" s="77">
@@ -13200,7 +13243,7 @@
         <v>8926</v>
       </c>
       <c r="AP28" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>5009</v>
       </c>
       <c r="AQ28" s="150">
@@ -13224,14 +13267,14 @@
       </c>
       <c r="AW28" s="110">
         <f t="shared" si="99"/>
-        <v>0.64855256475368206</v>
+        <v>0.58544946673438292</v>
       </c>
       <c r="AX28" s="110">
         <f t="shared" si="100"/>
-        <v>0.35144743524631794</v>
+        <v>0.41455053326561708</v>
       </c>
       <c r="AY28" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7876</v>
       </c>
       <c r="AZ28" s="112">
@@ -13239,10 +13282,11 @@
       </c>
       <c r="BA28" s="120">
         <f t="shared" si="101"/>
-        <v>5108</v>
+        <v>4611</v>
       </c>
       <c r="BB28" s="113">
-        <v>2768</v>
+        <f>2768+497</f>
+        <v>3265</v>
       </c>
       <c r="BC28" s="112">
         <v>3320</v>
@@ -13296,11 +13340,12 @@
       <c r="BR28" s="156">
         <v>0.80833333333333335</v>
       </c>
+      <c r="BU28" s="267"/>
     </row>
-    <row r="29" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46045</v>
       </c>
       <c r="C29" s="163"/>
@@ -13320,8 +13365,8 @@
         <f t="shared" si="86"/>
         <v>0.14180084745762711</v>
       </c>
-      <c r="H29" s="145">
-        <f t="shared" si="26"/>
+      <c r="H29" s="269">
+        <f t="shared" si="49"/>
         <v>6693</v>
       </c>
       <c r="I29" s="159">
@@ -13406,7 +13451,7 @@
         <v>6180</v>
       </c>
       <c r="AF29" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6180</v>
       </c>
       <c r="AG29" s="146">
@@ -13425,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="AL29" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46045</v>
       </c>
       <c r="AM29" s="77">
@@ -13440,7 +13485,7 @@
         <v>8650</v>
       </c>
       <c r="AP29" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4860</v>
       </c>
       <c r="AQ29" s="150">
@@ -13471,7 +13516,7 @@
         <v>0</v>
       </c>
       <c r="AY29" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7820</v>
       </c>
       <c r="AZ29" s="112">
@@ -13536,287 +13581,289 @@
       <c r="BR29" s="156">
         <v>0.78125</v>
       </c>
+      <c r="BU29" s="267"/>
     </row>
-    <row r="30" spans="1:70" s="307" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="272"/>
-      <c r="B30" s="273">
-        <f t="shared" si="49"/>
+    <row r="30" spans="1:73" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="213"/>
+      <c r="B30" s="214">
+        <f t="shared" si="48"/>
         <v>46046</v>
       </c>
-      <c r="C30" s="274"/>
-      <c r="D30" s="275">
+      <c r="C30" s="215"/>
+      <c r="D30" s="216">
         <f t="shared" si="22"/>
         <v>35598</v>
       </c>
-      <c r="E30" s="276">
+      <c r="E30" s="217">
         <f t="shared" si="85"/>
         <v>0.7890923647395921</v>
       </c>
-      <c r="F30" s="275">
+      <c r="F30" s="216">
         <f t="shared" si="24"/>
         <v>28090.11</v>
       </c>
-      <c r="G30" s="276">
+      <c r="G30" s="217">
         <f t="shared" si="86"/>
         <v>0.21090763526040787</v>
       </c>
-      <c r="H30" s="277">
-        <f t="shared" si="26"/>
+      <c r="H30" s="270">
+        <f t="shared" si="49"/>
         <v>7507.8899999999994</v>
       </c>
-      <c r="I30" s="278">
+      <c r="I30" s="219">
         <f t="shared" si="87"/>
         <v>8.2277122633939659E-2</v>
       </c>
-      <c r="J30" s="276">
+      <c r="J30" s="217">
         <f t="shared" si="88"/>
         <v>0.16694050510003733</v>
       </c>
-      <c r="K30" s="276">
+      <c r="K30" s="217">
         <f t="shared" si="89"/>
         <v>6.5493869790672898E-2</v>
       </c>
-      <c r="L30" s="279">
+      <c r="L30" s="220">
         <f t="shared" si="90"/>
         <v>0.70748082689066438</v>
       </c>
-      <c r="M30" s="277">
+      <c r="M30" s="218">
         <f t="shared" si="91"/>
         <v>2515.6230245327051</v>
       </c>
-      <c r="N30" s="277">
+      <c r="N30" s="218">
         <f t="shared" si="92"/>
         <v>5104.2059434336416</v>
       </c>
-      <c r="O30" s="277">
+      <c r="O30" s="218">
         <f t="shared" si="93"/>
         <v>2002.4750688498239</v>
       </c>
-      <c r="P30" s="277">
+      <c r="P30" s="218">
         <f t="shared" si="94"/>
         <v>21631.226282182062</v>
       </c>
-      <c r="Q30" s="273">
+      <c r="Q30" s="214">
         <f t="shared" si="50"/>
         <v>46046</v>
       </c>
-      <c r="R30" s="280">
+      <c r="R30" s="221">
         <v>35598</v>
       </c>
-      <c r="S30" s="281">
-        <v>0</v>
-      </c>
-      <c r="T30" s="281">
+      <c r="S30" s="222">
+        <v>0</v>
+      </c>
+      <c r="T30" s="222">
         <v>30575</v>
       </c>
-      <c r="U30" s="281">
+      <c r="U30" s="222">
         <v>3750</v>
       </c>
-      <c r="V30" s="282">
+      <c r="V30" s="223">
         <v>7309.54</v>
       </c>
-      <c r="W30" s="283">
+      <c r="W30" s="224">
         <v>0.57291666666666663</v>
       </c>
-      <c r="X30" s="282">
+      <c r="X30" s="223">
         <v>2292.96</v>
       </c>
-      <c r="Y30" s="283">
+      <c r="Y30" s="224">
         <v>0.84375</v>
       </c>
-      <c r="Z30" s="282">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="283">
+      <c r="Z30" s="223">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="224">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="AB30" s="273">
+      <c r="AB30" s="214">
         <f t="shared" si="51"/>
         <v>46046</v>
       </c>
-      <c r="AC30" s="284">
+      <c r="AC30" s="225">
         <f t="shared" si="95"/>
         <v>1</v>
       </c>
-      <c r="AD30" s="285">
+      <c r="AD30" s="226">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="286">
+      <c r="AE30" s="227">
         <v>2948</v>
       </c>
-      <c r="AF30" s="287">
+      <c r="AF30" s="228">
+        <f t="shared" si="36"/>
+        <v>2948</v>
+      </c>
+      <c r="AG30" s="218">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="229">
+        <v>1861.85</v>
+      </c>
+      <c r="AI30" s="230">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="AJ30" s="229">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="231">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="214">
         <f t="shared" si="37"/>
-        <v>2948</v>
-      </c>
-      <c r="AG30" s="277">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="288">
-        <v>1861.85</v>
-      </c>
-      <c r="AI30" s="289">
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="AJ30" s="288">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="290">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="273">
-        <f t="shared" si="38"/>
         <v>46046</v>
       </c>
-      <c r="AM30" s="291">
+      <c r="AM30" s="232">
         <f t="shared" si="97"/>
         <v>0.37174788932542008</v>
       </c>
-      <c r="AN30" s="284">
+      <c r="AN30" s="225">
         <f t="shared" si="98"/>
         <v>0.62825211067457998</v>
       </c>
-      <c r="AO30" s="292">
+      <c r="AO30" s="233">
         <v>5981.5</v>
       </c>
-      <c r="AP30" s="293">
-        <f t="shared" si="41"/>
+      <c r="AP30" s="234">
+        <f t="shared" si="40"/>
         <v>2223.61</v>
       </c>
-      <c r="AQ30" s="294">
+      <c r="AQ30" s="235">
         <v>3757.89</v>
       </c>
-      <c r="AR30" s="288">
+      <c r="AR30" s="229">
         <v>1674.84</v>
       </c>
-      <c r="AS30" s="295">
+      <c r="AS30" s="236">
         <v>0.9243055555555556</v>
       </c>
-      <c r="AT30" s="288">
+      <c r="AT30" s="229">
         <v>173.49</v>
       </c>
-      <c r="AU30" s="296">
+      <c r="AU30" s="237">
         <v>0.3125</v>
       </c>
-      <c r="AV30" s="273">
+      <c r="AV30" s="214">
         <f t="shared" si="52"/>
         <v>46046</v>
       </c>
-      <c r="AW30" s="297">
+      <c r="AW30" s="238">
         <f t="shared" si="99"/>
         <v>1</v>
       </c>
-      <c r="AX30" s="297">
+      <c r="AX30" s="238">
         <f t="shared" si="100"/>
         <v>0</v>
       </c>
-      <c r="AY30" s="298">
-        <f t="shared" si="44"/>
+      <c r="AY30" s="239">
+        <f t="shared" si="43"/>
         <v>1551.5</v>
       </c>
-      <c r="AZ30" s="299">
+      <c r="AZ30" s="240">
         <v>1551.5</v>
       </c>
-      <c r="BA30" s="300">
+      <c r="BA30" s="241">
         <f t="shared" si="101"/>
         <v>1551.5</v>
       </c>
-      <c r="BB30" s="298">
-        <v>0</v>
-      </c>
-      <c r="BC30" s="299">
+      <c r="BB30" s="239">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="240">
         <v>1875.84</v>
       </c>
-      <c r="BD30" s="301">
+      <c r="BD30" s="242">
         <v>0.53125</v>
       </c>
-      <c r="BE30" s="302">
-        <v>0</v>
-      </c>
-      <c r="BF30" s="301">
-        <v>0</v>
-      </c>
-      <c r="BG30" s="302">
-        <v>0</v>
-      </c>
-      <c r="BH30" s="301">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="273">
+      <c r="BE30" s="243">
+        <v>0</v>
+      </c>
+      <c r="BF30" s="242">
+        <v>0</v>
+      </c>
+      <c r="BG30" s="243">
+        <v>0</v>
+      </c>
+      <c r="BH30" s="242">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="214">
         <f t="shared" si="53"/>
         <v>46046</v>
       </c>
-      <c r="BJ30" s="303">
+      <c r="BJ30" s="244">
         <f t="shared" si="102"/>
         <v>0.60809305881503628</v>
       </c>
-      <c r="BK30" s="284">
+      <c r="BK30" s="225">
         <f t="shared" si="103"/>
         <v>0.39190694118496378</v>
       </c>
-      <c r="BL30" s="304">
+      <c r="BL30" s="245">
         <f t="shared" si="104"/>
         <v>25349.129999999997</v>
       </c>
-      <c r="BM30" s="277">
+      <c r="BM30" s="218">
         <v>15414.63</v>
       </c>
-      <c r="BN30" s="277">
+      <c r="BN30" s="218">
         <v>9934.5</v>
       </c>
-      <c r="BO30" s="305">
+      <c r="BO30" s="246">
         <v>2730.84</v>
       </c>
-      <c r="BP30" s="289">
+      <c r="BP30" s="230">
         <v>0.80208333333333337</v>
       </c>
-      <c r="BQ30" s="306">
+      <c r="BQ30" s="247">
         <v>1824.37</v>
       </c>
-      <c r="BR30" s="289">
+      <c r="BR30" s="230">
         <v>0.80208333333333337</v>
       </c>
+      <c r="BU30" s="267"/>
     </row>
-    <row r="31" spans="1:70" s="271" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="244"/>
-      <c r="B31" s="245">
-        <f t="shared" si="49"/>
+    <row r="31" spans="1:73" s="212" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="185"/>
+      <c r="B31" s="186">
+        <f t="shared" si="48"/>
         <v>46047</v>
       </c>
-      <c r="C31" s="325"/>
-      <c r="D31" s="247">
+      <c r="C31" s="266"/>
+      <c r="D31" s="188">
         <f t="shared" si="22"/>
         <v>27334</v>
       </c>
-      <c r="E31" s="248">
+      <c r="E31" s="189">
         <f t="shared" si="85"/>
         <v>0.72663788688080777</v>
       </c>
-      <c r="F31" s="247">
+      <c r="F31" s="188">
         <f t="shared" si="24"/>
         <v>19861.919999999998</v>
       </c>
-      <c r="G31" s="248">
+      <c r="G31" s="189">
         <f t="shared" si="86"/>
         <v>0.27336211311919223</v>
       </c>
-      <c r="H31" s="154">
-        <f t="shared" si="26"/>
+      <c r="H31" s="268">
+        <f t="shared" si="49"/>
         <v>7472.08</v>
       </c>
-      <c r="I31" s="249">
+      <c r="I31" s="190">
         <f t="shared" si="87"/>
         <v>8.0814329368973814E-2</v>
       </c>
-      <c r="J31" s="248">
+      <c r="J31" s="189">
         <f t="shared" si="88"/>
         <v>0.21075679421764754</v>
       </c>
-      <c r="K31" s="248">
+      <c r="K31" s="189">
         <f t="shared" si="89"/>
         <v>0.14936154843096014</v>
       </c>
-      <c r="L31" s="250">
+      <c r="L31" s="191">
         <f t="shared" si="90"/>
         <v>0.5994361214083167</v>
       </c>
@@ -13836,7 +13883,7 @@
         <f t="shared" si="94"/>
         <v>13569.735198380769</v>
       </c>
-      <c r="Q31" s="245">
+      <c r="Q31" s="186">
         <f t="shared" si="50"/>
         <v>46047</v>
       </c>
@@ -13870,131 +13917,131 @@
       <c r="AA31" s="141">
         <v>0.95833333333333337</v>
       </c>
-      <c r="AB31" s="245">
+      <c r="AB31" s="186">
         <f t="shared" si="51"/>
         <v>46047</v>
       </c>
-      <c r="AC31" s="251">
+      <c r="AC31" s="192">
         <f t="shared" si="95"/>
         <v>1</v>
       </c>
-      <c r="AD31" s="252">
+      <c r="AD31" s="193">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
-      <c r="AE31" s="253">
+      <c r="AE31" s="194">
         <v>2085</v>
       </c>
-      <c r="AF31" s="254">
-        <f t="shared" si="37"/>
+      <c r="AF31" s="195">
+        <f t="shared" si="36"/>
         <v>2085</v>
       </c>
       <c r="AG31" s="154">
         <v>0</v>
       </c>
-      <c r="AH31" s="255">
+      <c r="AH31" s="196">
         <v>1633.06</v>
       </c>
       <c r="AI31" s="156">
         <v>0.93958333333333333</v>
       </c>
-      <c r="AJ31" s="255">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="256">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="245">
-        <f t="shared" si="38"/>
+      <c r="AJ31" s="196">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="197">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="186">
+        <f t="shared" si="37"/>
         <v>46047</v>
       </c>
-      <c r="AM31" s="257">
+      <c r="AM31" s="198">
         <f t="shared" si="97"/>
         <v>0.31290482758620691</v>
       </c>
-      <c r="AN31" s="251">
+      <c r="AN31" s="192">
         <f t="shared" si="98"/>
         <v>0.68709517241379314</v>
       </c>
-      <c r="AO31" s="258">
+      <c r="AO31" s="199">
         <v>5437.5</v>
       </c>
-      <c r="AP31" s="259">
-        <f t="shared" si="41"/>
+      <c r="AP31" s="200">
+        <f t="shared" si="40"/>
         <v>1701.42</v>
       </c>
-      <c r="AQ31" s="260">
+      <c r="AQ31" s="201">
         <v>3736.08</v>
       </c>
-      <c r="AR31" s="255">
+      <c r="AR31" s="196">
         <v>1668.27</v>
       </c>
-      <c r="AS31" s="261">
+      <c r="AS31" s="202">
         <v>0.93680555555555556</v>
       </c>
-      <c r="AT31" s="255">
+      <c r="AT31" s="196">
         <v>193.68</v>
       </c>
-      <c r="AU31" s="262">
+      <c r="AU31" s="203">
         <v>0.875</v>
       </c>
-      <c r="AV31" s="245">
+      <c r="AV31" s="186">
         <f t="shared" si="52"/>
         <v>46047</v>
       </c>
-      <c r="AW31" s="263">
+      <c r="AW31" s="204">
         <f t="shared" si="99"/>
         <v>1</v>
       </c>
-      <c r="AX31" s="263">
+      <c r="AX31" s="204">
         <f t="shared" si="100"/>
         <v>0</v>
       </c>
-      <c r="AY31" s="264">
-        <f t="shared" si="44"/>
+      <c r="AY31" s="205">
+        <f t="shared" si="43"/>
         <v>2812</v>
       </c>
-      <c r="AZ31" s="265">
+      <c r="AZ31" s="206">
         <v>2812</v>
       </c>
-      <c r="BA31" s="266">
+      <c r="BA31" s="207">
         <f t="shared" si="101"/>
         <v>2812</v>
       </c>
-      <c r="BB31" s="264">
-        <v>0</v>
-      </c>
-      <c r="BC31" s="265">
+      <c r="BB31" s="205">
+        <v>0</v>
+      </c>
+      <c r="BC31" s="206">
         <v>3350.08</v>
       </c>
-      <c r="BD31" s="267">
+      <c r="BD31" s="208">
         <v>0.90625</v>
       </c>
-      <c r="BE31" s="268">
-        <v>0</v>
-      </c>
-      <c r="BF31" s="267">
-        <v>0</v>
-      </c>
-      <c r="BG31" s="268">
-        <v>0</v>
-      </c>
-      <c r="BH31" s="267">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="245">
+      <c r="BE31" s="209">
+        <v>0</v>
+      </c>
+      <c r="BF31" s="208">
+        <v>0</v>
+      </c>
+      <c r="BG31" s="209">
+        <v>0</v>
+      </c>
+      <c r="BH31" s="208">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="186">
         <f t="shared" si="53"/>
         <v>46047</v>
       </c>
-      <c r="BJ31" s="269">
+      <c r="BJ31" s="210">
         <f t="shared" si="102"/>
         <v>0.60886832395970869</v>
       </c>
-      <c r="BK31" s="251">
+      <c r="BK31" s="192">
         <f t="shared" si="103"/>
         <v>0.39113167604029131</v>
       </c>
-      <c r="BL31" s="270">
+      <c r="BL31" s="211">
         <f t="shared" si="104"/>
         <v>15465.38</v>
       </c>
@@ -14016,11 +14063,12 @@
       <c r="BR31" s="156">
         <v>0.9604166666666667</v>
       </c>
+      <c r="BU31" s="267"/>
     </row>
-    <row r="32" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46048</v>
       </c>
       <c r="C32" s="163"/>
@@ -14040,8 +14088,8 @@
         <f t="shared" si="86"/>
         <v>0.14753634894991924</v>
       </c>
-      <c r="H32" s="145">
-        <f t="shared" si="26"/>
+      <c r="H32" s="269">
+        <f t="shared" si="49"/>
         <v>7306</v>
       </c>
       <c r="I32" s="159">
@@ -14126,7 +14174,7 @@
         <v>6150</v>
       </c>
       <c r="AF32" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6150</v>
       </c>
       <c r="AG32" s="146">
@@ -14145,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="AL32" s="167">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46048</v>
       </c>
       <c r="AM32" s="77">
@@ -14160,7 +14208,7 @@
         <v>8720</v>
       </c>
       <c r="AP32" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4860</v>
       </c>
       <c r="AQ32" s="150">
@@ -14191,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="AY32" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7850</v>
       </c>
       <c r="AZ32" s="112">
@@ -14256,11 +14304,12 @@
       <c r="BR32" s="156">
         <v>0.9375</v>
       </c>
+      <c r="BU32" s="267"/>
     </row>
-    <row r="33" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46049</v>
       </c>
       <c r="C33" s="163"/>
@@ -14270,19 +14319,19 @@
       </c>
       <c r="E33" s="158">
         <f t="shared" si="85"/>
-        <v>0.8652087475149105</v>
+        <v>0.85532803180914518</v>
       </c>
       <c r="F33" s="87">
         <f t="shared" si="24"/>
-        <v>43520</v>
+        <v>43023</v>
       </c>
       <c r="G33" s="158">
         <f t="shared" si="86"/>
-        <v>0.13479125248508947</v>
-      </c>
-      <c r="H33" s="145">
-        <f t="shared" si="26"/>
-        <v>6780</v>
+        <v>0.14467196819085487</v>
+      </c>
+      <c r="H33" s="269">
+        <f t="shared" si="49"/>
+        <v>7277</v>
       </c>
       <c r="I33" s="159">
         <f t="shared" si="87"/>
@@ -14366,7 +14415,7 @@
         <v>6230</v>
       </c>
       <c r="AF33" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6230</v>
       </c>
       <c r="AG33" s="146">
@@ -14385,7 +14434,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="167">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46049</v>
       </c>
       <c r="AM33" s="77">
@@ -14400,7 +14449,7 @@
         <v>8890</v>
       </c>
       <c r="AP33" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4940</v>
       </c>
       <c r="AQ33" s="150">
@@ -14424,14 +14473,14 @@
       </c>
       <c r="AW33" s="168">
         <f t="shared" si="99"/>
-        <v>0.64040660736975863</v>
+        <v>0.57725540025412958</v>
       </c>
       <c r="AX33" s="168">
         <f t="shared" si="100"/>
-        <v>0.35959339263024143</v>
+        <v>0.42274459974587042</v>
       </c>
       <c r="AY33" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7870</v>
       </c>
       <c r="AZ33" s="112">
@@ -14439,10 +14488,11 @@
       </c>
       <c r="BA33" s="169">
         <f t="shared" si="101"/>
-        <v>5040</v>
+        <v>4543</v>
       </c>
       <c r="BB33" s="113">
-        <v>2830</v>
+        <f>2830+497</f>
+        <v>3327</v>
       </c>
       <c r="BC33" s="112">
         <v>3450</v>
@@ -14496,11 +14546,12 @@
       <c r="BR33" s="156">
         <v>0.89583333333333337</v>
       </c>
+      <c r="BU33" s="267"/>
     </row>
-    <row r="34" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
       <c r="B34" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46050</v>
       </c>
       <c r="C34" s="163"/>
@@ -14510,19 +14561,19 @@
       </c>
       <c r="E34" s="158">
         <f t="shared" si="85"/>
-        <v>0.86242394939360978</v>
+        <v>0.85241145896289139</v>
       </c>
       <c r="F34" s="87">
         <f t="shared" si="24"/>
-        <v>42809</v>
+        <v>42312</v>
       </c>
       <c r="G34" s="158">
         <f t="shared" si="86"/>
-        <v>0.13757605060639028</v>
-      </c>
-      <c r="H34" s="145">
-        <f t="shared" si="26"/>
-        <v>6829</v>
+        <v>0.14758854103710867</v>
+      </c>
+      <c r="H34" s="269">
+        <f t="shared" si="49"/>
+        <v>7326</v>
       </c>
       <c r="I34" s="159">
         <f t="shared" si="87"/>
@@ -14606,7 +14657,7 @@
         <v>6111</v>
       </c>
       <c r="AF34" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>6111</v>
       </c>
       <c r="AG34" s="146">
@@ -14625,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="AL34" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46050</v>
       </c>
       <c r="AM34" s="77">
@@ -14640,7 +14691,7 @@
         <v>8674</v>
       </c>
       <c r="AP34" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4698</v>
       </c>
       <c r="AQ34" s="150">
@@ -14664,14 +14715,14 @@
       </c>
       <c r="AW34" s="110">
         <f t="shared" si="99"/>
-        <v>0.63693051667090861</v>
+        <v>0.57368287095953163</v>
       </c>
       <c r="AX34" s="110">
         <f t="shared" si="100"/>
-        <v>0.36306948332909139</v>
+        <v>0.42631712904046831</v>
       </c>
       <c r="AY34" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7858</v>
       </c>
       <c r="AZ34" s="112">
@@ -14679,10 +14730,11 @@
       </c>
       <c r="BA34" s="120">
         <f t="shared" si="101"/>
-        <v>5005</v>
+        <v>4508</v>
       </c>
       <c r="BB34" s="113">
-        <v>2853</v>
+        <f>2853+497</f>
+        <v>3350</v>
       </c>
       <c r="BC34" s="112">
         <v>3047</v>
@@ -14736,11 +14788,12 @@
       <c r="BR34" s="156">
         <v>0.78263888888888888</v>
       </c>
+      <c r="BU34" s="267"/>
     </row>
-    <row r="35" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
       <c r="B35" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46051</v>
       </c>
       <c r="C35" s="163"/>
@@ -14750,19 +14803,19 @@
       </c>
       <c r="E35" s="158">
         <f t="shared" si="85"/>
-        <v>0.85993239941358524</v>
+        <v>0.84981267307379049</v>
       </c>
       <c r="F35" s="87">
         <f t="shared" si="24"/>
-        <v>42233</v>
+        <v>41736</v>
       </c>
       <c r="G35" s="158">
         <f t="shared" si="86"/>
-        <v>0.14006760058641474</v>
-      </c>
-      <c r="H35" s="145">
-        <f t="shared" si="26"/>
-        <v>6879</v>
+        <v>0.15018732692620948</v>
+      </c>
+      <c r="H35" s="269">
+        <f t="shared" si="49"/>
+        <v>7376</v>
       </c>
       <c r="I35" s="159">
         <f t="shared" si="87"/>
@@ -14846,7 +14899,7 @@
         <v>5946</v>
       </c>
       <c r="AF35" s="118">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>5946</v>
       </c>
       <c r="AG35" s="146">
@@ -14865,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="AL35" s="56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>46051</v>
       </c>
       <c r="AM35" s="77">
@@ -14880,7 +14933,7 @@
         <v>8701</v>
       </c>
       <c r="AP35" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>4660</v>
       </c>
       <c r="AQ35" s="150">
@@ -14904,14 +14957,14 @@
       </c>
       <c r="AW35" s="110">
         <f t="shared" si="99"/>
-        <v>0.62867983776004188</v>
+        <v>0.56365301583147975</v>
       </c>
       <c r="AX35" s="110">
         <f t="shared" si="100"/>
-        <v>0.37132016223995812</v>
+        <v>0.43634698416852019</v>
       </c>
       <c r="AY35" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>7643</v>
       </c>
       <c r="AZ35" s="112">
@@ -14919,10 +14972,11 @@
       </c>
       <c r="BA35" s="120">
         <f t="shared" si="101"/>
-        <v>4805</v>
+        <v>4308</v>
       </c>
       <c r="BB35" s="113">
-        <v>2838</v>
+        <f>2838+497</f>
+        <v>3335</v>
       </c>
       <c r="BC35" s="112">
         <v>3069</v>
@@ -14976,11 +15030,12 @@
       <c r="BR35" s="156">
         <v>0.74722222222222223</v>
       </c>
+      <c r="BU35" s="267"/>
     </row>
-    <row r="36" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
       <c r="B36" s="56">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>46052</v>
       </c>
       <c r="C36" s="163"/>
@@ -14990,19 +15045,19 @@
       </c>
       <c r="E36" s="158">
         <f t="shared" si="85"/>
-        <v>0.87838495575221243</v>
+        <v>0.86738938053097348</v>
       </c>
       <c r="F36" s="87">
         <f t="shared" si="24"/>
-        <v>39703</v>
+        <v>39206</v>
       </c>
       <c r="G36" s="158">
         <f t="shared" si="86"/>
-        <v>0.12161504424778762</v>
-      </c>
-      <c r="H36" s="145">
-        <f t="shared" si="26"/>
-        <v>5497</v>
+        <v>0.13261061946902655</v>
+      </c>
+      <c r="H36" s="269">
+        <f t="shared" si="49"/>
+        <v>5994</v>
       </c>
       <c r="I36" s="159">
         <f t="shared" si="87"/>
@@ -15086,26 +15141,26 @@
         <v>2855</v>
       </c>
       <c r="AF36" s="118">
+        <f t="shared" si="36"/>
+        <v>2855</v>
+      </c>
+      <c r="AG36" s="146">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="147">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="148">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="147">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="164">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="56">
         <f t="shared" si="37"/>
-        <v>2855</v>
-      </c>
-      <c r="AG36" s="146">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="147">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="148">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="147">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="164">
-        <v>0</v>
-      </c>
-      <c r="AL36" s="56">
-        <f t="shared" si="38"/>
         <v>46052</v>
       </c>
       <c r="AM36" s="77">
@@ -15120,7 +15175,7 @@
         <v>4908</v>
       </c>
       <c r="AP36" s="117">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>2246</v>
       </c>
       <c r="AQ36" s="150">
@@ -15144,14 +15199,14 @@
       </c>
       <c r="AW36" s="110">
         <f t="shared" si="99"/>
-        <v>0.70326564789616919</v>
+        <v>0.6512455516014235</v>
       </c>
       <c r="AX36" s="110">
         <f t="shared" si="100"/>
-        <v>0.29673435210383087</v>
+        <v>0.3487544483985765</v>
       </c>
       <c r="AY36" s="111">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>9554</v>
       </c>
       <c r="AZ36" s="112">
@@ -15159,10 +15214,11 @@
       </c>
       <c r="BA36" s="120">
         <f t="shared" si="101"/>
-        <v>6719</v>
+        <v>6222</v>
       </c>
       <c r="BB36" s="113">
-        <v>2835</v>
+        <f>2835+497</f>
+        <v>3332</v>
       </c>
       <c r="BC36" s="112">
         <v>5444</v>
@@ -15216,292 +15272,329 @@
       <c r="BR36" s="156">
         <v>0.71736111111111112</v>
       </c>
+      <c r="BU36" s="267"/>
     </row>
-    <row r="37" spans="1:70" s="307" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="272"/>
-      <c r="B37" s="273">
-        <f t="shared" si="49"/>
+    <row r="37" spans="1:73" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="213"/>
+      <c r="B37" s="214">
+        <f t="shared" si="48"/>
         <v>46053</v>
       </c>
-      <c r="C37" s="274"/>
-      <c r="D37" s="275">
+      <c r="C37" s="215"/>
+      <c r="D37" s="216">
         <f t="shared" si="22"/>
         <v>32388</v>
       </c>
-      <c r="E37" s="276">
+      <c r="E37" s="217">
         <f t="shared" ref="E37" si="105">F37/D37</f>
-        <v>0.82592318142521925</v>
-      </c>
-      <c r="F37" s="275">
+        <v>0.81057799184883295</v>
+      </c>
+      <c r="F37" s="216">
         <f t="shared" si="24"/>
-        <v>26750</v>
-      </c>
-      <c r="G37" s="276">
+        <v>26253</v>
+      </c>
+      <c r="G37" s="217">
         <f t="shared" ref="G37" si="106">H37/D37</f>
-        <v>0.17407681857478077</v>
-      </c>
-      <c r="H37" s="277">
-        <f t="shared" si="26"/>
-        <v>5638</v>
-      </c>
-      <c r="I37" s="278">
+        <v>0.18942200815116711</v>
+      </c>
+      <c r="H37" s="270">
+        <f>U37+AG37+AQ37+BB37</f>
+        <v>6135</v>
+      </c>
+      <c r="I37" s="219">
         <f t="shared" ref="I37" si="107">AE37/(AE37+AO37+BL37+AY37)</f>
         <v>8.3172573444303594E-2</v>
       </c>
-      <c r="J37" s="276">
+      <c r="J37" s="217">
         <f t="shared" ref="J37" si="108">AO37/(AE37+AO37+BL37+AY37)</f>
         <v>0.13864851457862537</v>
       </c>
-      <c r="K37" s="276">
+      <c r="K37" s="217">
         <f t="shared" ref="K37" si="109">AY37/(AF37+AP37+BM37+AZ37+AY37)</f>
         <v>0.17017044480263382</v>
       </c>
-      <c r="L37" s="279">
+      <c r="L37" s="220">
         <f t="shared" ref="L37" si="110">BL37/(AE37+AO37+BL37+AY37)</f>
         <v>0.64143195722868329</v>
       </c>
-      <c r="M37" s="277">
+      <c r="M37" s="218">
         <f>(S37+T37)*I37</f>
         <v>2625.924488783553</v>
       </c>
-      <c r="N37" s="277">
+      <c r="N37" s="218">
         <f>(S37+T37)*J37</f>
         <v>4377.4109022763605</v>
       </c>
-      <c r="O37" s="277">
+      <c r="O37" s="218">
         <f>(S37+T37)*K37</f>
         <v>5372.6212833087548</v>
       </c>
-      <c r="P37" s="277">
+      <c r="P37" s="218">
         <f>(S37+T37)*L37</f>
         <v>20251.289753623991</v>
       </c>
-      <c r="Q37" s="273">
+      <c r="Q37" s="214">
         <f t="shared" si="50"/>
         <v>46053</v>
       </c>
-      <c r="R37" s="280">
+      <c r="R37" s="221">
         <v>32388</v>
       </c>
-      <c r="S37" s="281">
-        <v>0</v>
-      </c>
-      <c r="T37" s="281">
+      <c r="S37" s="222">
+        <v>0</v>
+      </c>
+      <c r="T37" s="222">
         <v>31572</v>
       </c>
-      <c r="U37" s="281">
-        <v>0</v>
-      </c>
-      <c r="V37" s="282">
+      <c r="U37" s="222">
+        <v>0</v>
+      </c>
+      <c r="V37" s="223">
         <v>6796</v>
       </c>
-      <c r="W37" s="283">
+      <c r="W37" s="224">
         <v>0.39583333333333331</v>
       </c>
-      <c r="X37" s="282">
+      <c r="X37" s="223">
         <v>2147</v>
       </c>
-      <c r="Y37" s="283">
+      <c r="Y37" s="224">
         <v>0.88541666666666663</v>
       </c>
-      <c r="Z37" s="282">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="283">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="273">
+      <c r="Z37" s="223">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="224">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="214">
         <f t="shared" si="51"/>
         <v>46053</v>
       </c>
-      <c r="AC37" s="284">
+      <c r="AC37" s="225">
         <f t="shared" ref="AC37" si="111">+AF37/AE37</f>
         <v>1</v>
       </c>
-      <c r="AD37" s="285">
+      <c r="AD37" s="226">
         <f t="shared" ref="AD37" si="112">+AG37/AE37</f>
         <v>0</v>
       </c>
-      <c r="AE37" s="286">
+      <c r="AE37" s="227">
         <v>3018</v>
       </c>
-      <c r="AF37" s="287">
+      <c r="AF37" s="228">
         <f t="shared" ref="AF37" si="113">+AE37-AG37</f>
         <v>3018</v>
       </c>
-      <c r="AG37" s="277">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="288">
+      <c r="AG37" s="218">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="229">
         <v>1643</v>
       </c>
-      <c r="AI37" s="289">
+      <c r="AI37" s="230">
         <v>0.93263888888888891</v>
       </c>
-      <c r="AJ37" s="288">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="290">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="273">
-        <f t="shared" si="38"/>
+      <c r="AJ37" s="229">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="231">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="214">
+        <f t="shared" si="37"/>
         <v>46053</v>
       </c>
-      <c r="AM37" s="291">
+      <c r="AM37" s="232">
         <f t="shared" ref="AM37" si="114">+AP37/AO37</f>
         <v>0.41800834824090638</v>
       </c>
-      <c r="AN37" s="284">
+      <c r="AN37" s="225">
         <f t="shared" ref="AN37" si="115">+AQ37/AO37</f>
         <v>0.58199165175909362</v>
       </c>
-      <c r="AO37" s="292">
+      <c r="AO37" s="233">
         <v>5031</v>
       </c>
-      <c r="AP37" s="293">
+      <c r="AP37" s="234">
         <f t="shared" ref="AP37" si="116">AO37-AQ37</f>
         <v>2103</v>
       </c>
-      <c r="AQ37" s="294">
+      <c r="AQ37" s="235">
         <v>2928</v>
       </c>
-      <c r="AR37" s="288">
+      <c r="AR37" s="229">
         <v>1858</v>
       </c>
-      <c r="AS37" s="295">
+      <c r="AS37" s="236">
         <v>0.35208333333333336</v>
       </c>
-      <c r="AT37" s="288">
+      <c r="AT37" s="229">
         <v>190</v>
       </c>
-      <c r="AU37" s="296">
+      <c r="AU37" s="237">
         <v>0.89583333333333337</v>
       </c>
-      <c r="AV37" s="273">
+      <c r="AV37" s="214">
         <f t="shared" si="52"/>
         <v>46053</v>
       </c>
-      <c r="AW37" s="297">
+      <c r="AW37" s="238">
         <f t="shared" ref="AW37" si="117">BA37/AZ37</f>
-        <v>0.45384925433293027</v>
-      </c>
-      <c r="AX37" s="297">
+        <v>0.35368802902055624</v>
+      </c>
+      <c r="AX37" s="238">
         <f t="shared" ref="AX37" si="118">BB37/AZ37</f>
-        <v>0.54615074566706978</v>
-      </c>
-      <c r="AY37" s="298">
+        <v>0.64631197097944382</v>
+      </c>
+      <c r="AY37" s="239">
         <f t="shared" ref="AY37" si="119">BA37+BB37</f>
         <v>4962</v>
       </c>
-      <c r="AZ37" s="299">
+      <c r="AZ37" s="240">
         <v>4962</v>
       </c>
-      <c r="BA37" s="300">
+      <c r="BA37" s="241">
         <f t="shared" ref="BA37" si="120">AZ37-BB37</f>
-        <v>2252</v>
-      </c>
-      <c r="BB37" s="298">
-        <v>2710</v>
-      </c>
-      <c r="BC37" s="299">
+        <v>1755</v>
+      </c>
+      <c r="BB37" s="239">
+        <f>2710+497</f>
+        <v>3207</v>
+      </c>
+      <c r="BC37" s="240">
         <v>1583</v>
       </c>
-      <c r="BD37" s="301">
+      <c r="BD37" s="242">
         <v>0.88541666666666663</v>
       </c>
-      <c r="BE37" s="302">
-        <v>0</v>
-      </c>
-      <c r="BF37" s="301">
-        <v>0</v>
-      </c>
-      <c r="BG37" s="302">
+      <c r="BE37" s="243">
+        <v>0</v>
+      </c>
+      <c r="BF37" s="242">
+        <v>0</v>
+      </c>
+      <c r="BG37" s="243">
         <v>158</v>
       </c>
-      <c r="BH37" s="301">
+      <c r="BH37" s="242">
         <v>0.23958333333333334</v>
       </c>
-      <c r="BI37" s="273">
+      <c r="BI37" s="214">
         <f t="shared" si="53"/>
         <v>46053</v>
       </c>
-      <c r="BJ37" s="303">
+      <c r="BJ37" s="244">
         <f t="shared" ref="BJ37" si="121">+BM37/BL37</f>
         <v>0.60640171858216974</v>
       </c>
-      <c r="BK37" s="284">
+      <c r="BK37" s="225">
         <f t="shared" ref="BK37" si="122">+BN37/BL37</f>
         <v>0.39359828141783026</v>
       </c>
-      <c r="BL37" s="304">
+      <c r="BL37" s="245">
         <f t="shared" ref="BL37" si="123">BM37+BN37</f>
         <v>23275</v>
       </c>
-      <c r="BM37" s="277">
+      <c r="BM37" s="218">
         <v>14114</v>
       </c>
-      <c r="BN37" s="277">
+      <c r="BN37" s="218">
         <v>9161</v>
       </c>
-      <c r="BO37" s="305">
+      <c r="BO37" s="246">
         <v>2561</v>
       </c>
-      <c r="BP37" s="289">
+      <c r="BP37" s="230">
         <v>0.37430555555555556</v>
       </c>
-      <c r="BQ37" s="306">
+      <c r="BQ37" s="247">
         <v>1677</v>
       </c>
-      <c r="BR37" s="289">
+      <c r="BR37" s="230">
         <v>0.80972222222222223</v>
       </c>
+      <c r="BU37" s="267"/>
     </row>
-    <row r="38" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="D38" s="175">
+        <f>SUM(D7:D37)</f>
+        <v>1383925</v>
+      </c>
+      <c r="F38" s="175">
+        <f>SUM(F7:F37)</f>
+        <v>1166057.4900000002</v>
+      </c>
+      <c r="H38" s="175">
+        <f>SUM(H7:H37)</f>
+        <v>217867.50999999998</v>
+      </c>
       <c r="R38" s="175" t="e">
         <f>#REF!-S39</f>
         <v>#REF!</v>
       </c>
+      <c r="BU38" s="267"/>
     </row>
-    <row r="39" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
       <c r="S39" s="176">
         <f>R36-T36</f>
         <v>-348</v>
       </c>
       <c r="T39" s="176"/>
-      <c r="U39" s="175"/>
+      <c r="U39" s="175">
+        <f>AVERAGE(U29:U32)</f>
+        <v>3458.75</v>
+      </c>
+      <c r="BB39" s="175">
+        <f>AVERAGE(BB33:BB37,BB20:BB28,BB7:BB18)</f>
+        <v>3257.9926923076923</v>
+      </c>
+      <c r="BC39" s="175"/>
+      <c r="BU39" s="267"/>
     </row>
-    <row r="40" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="AP40" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ40" s="175">
-        <f>AVERAGE(AQ8,AQ11:AQ15,AQ18:AQ22,AQ25:AQ29,AQ32:AQ35)</f>
-        <v>3919.55</v>
-      </c>
+    <row r="40" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AQ40" s="175"/>
+      <c r="BB40" s="175">
+        <f>U39-BB39</f>
+        <v>200.75730769230768</v>
+      </c>
+      <c r="BC40" s="175"/>
+      <c r="BU40" s="267"/>
     </row>
-    <row r="41" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:73" x14ac:dyDescent="0.25">
       <c r="S41" s="176"/>
       <c r="T41" s="175"/>
-      <c r="AP41" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ41" s="175">
-        <f>AVERAGE(AQ9,AQ16,AQ23,AQ30)</f>
-        <v>3743.4724999999999</v>
-      </c>
+      <c r="AQ41" s="175"/>
+      <c r="BB41" s="14">
+        <v>497</v>
+      </c>
+      <c r="BU41" s="267"/>
     </row>
-    <row r="42" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="AP42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ42" s="175">
-        <f>AVERAGE(AQ7,AQ10,AQ17,AQ24,AQ31)</f>
-        <v>3677.5860000000002</v>
+    <row r="42" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AQ42" s="175"/>
+      <c r="BB42" s="175">
+        <f>BB40+BB41</f>
+        <v>697.75730769230768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -15518,22 +15611,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -15566,96 +15643,96 @@
       <c r="C1" s="15"/>
     </row>
     <row r="2" spans="2:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="221" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="224" t="s">
+      <c r="B2" s="307" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="310" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226"/>
-      <c r="J2" s="224" t="s">
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="312"/>
+      <c r="J2" s="310" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="225"/>
-      <c r="L2" s="226"/>
-      <c r="N2" s="224" t="s">
+      <c r="K2" s="311"/>
+      <c r="L2" s="312"/>
+      <c r="N2" s="310" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="225"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="225"/>
-      <c r="T2" s="226"/>
-      <c r="V2" s="230" t="s">
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="312"/>
+      <c r="V2" s="316" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="231"/>
-      <c r="X2" s="232"/>
+      <c r="W2" s="317"/>
+      <c r="X2" s="318"/>
     </row>
     <row r="3" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="222"/>
-      <c r="D3" s="227"/>
-      <c r="E3" s="228"/>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="229"/>
-      <c r="J3" s="227"/>
-      <c r="K3" s="228"/>
-      <c r="L3" s="229"/>
-      <c r="N3" s="227"/>
-      <c r="O3" s="228"/>
-      <c r="P3" s="228"/>
-      <c r="Q3" s="228"/>
-      <c r="R3" s="228"/>
-      <c r="S3" s="228"/>
-      <c r="T3" s="229"/>
-      <c r="V3" s="233"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="235"/>
+      <c r="B3" s="308"/>
+      <c r="D3" s="313"/>
+      <c r="E3" s="314"/>
+      <c r="F3" s="314"/>
+      <c r="G3" s="314"/>
+      <c r="H3" s="315"/>
+      <c r="J3" s="313"/>
+      <c r="K3" s="314"/>
+      <c r="L3" s="315"/>
+      <c r="N3" s="313"/>
+      <c r="O3" s="314"/>
+      <c r="P3" s="314"/>
+      <c r="Q3" s="314"/>
+      <c r="R3" s="314"/>
+      <c r="S3" s="314"/>
+      <c r="T3" s="315"/>
+      <c r="V3" s="319"/>
+      <c r="W3" s="320"/>
+      <c r="X3" s="321"/>
     </row>
     <row r="4" spans="2:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="222"/>
-      <c r="D4" s="236" t="s">
+      <c r="B4" s="308"/>
+      <c r="D4" s="322" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="237"/>
-      <c r="F4" s="236" t="s">
+      <c r="E4" s="323"/>
+      <c r="F4" s="322" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="238"/>
-      <c r="H4" s="239"/>
-      <c r="J4" s="236" t="s">
+      <c r="G4" s="324"/>
+      <c r="H4" s="325"/>
+      <c r="J4" s="322" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="237"/>
+      <c r="K4" s="323"/>
       <c r="L4" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="219" t="s">
+      <c r="N4" s="305" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="240"/>
-      <c r="P4" s="241"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="236" t="s">
+      <c r="O4" s="326"/>
+      <c r="P4" s="327"/>
+      <c r="Q4" s="328"/>
+      <c r="R4" s="322" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="243"/>
-      <c r="T4" s="239"/>
-      <c r="V4" s="219" t="s">
+      <c r="S4" s="329"/>
+      <c r="T4" s="325"/>
+      <c r="V4" s="305" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="220"/>
+      <c r="W4" s="306"/>
       <c r="X4" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:27" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="223"/>
+      <c r="B5" s="309"/>
       <c r="D5" s="17" t="s">
         <v>43</v>
       </c>
@@ -19918,15 +19995,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
@@ -19946,14 +20014,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED709115-1C3D-4AF3-8A87-7ADC8EF91565}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED709115-1C3D-4AF3-8A87-7ADC8EF91565}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BCC3370-B7AD-4715-B42A-F82531128245}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{750CB55E-BD40-466D-ABC6-DA7CA47DDF54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{750CB55E-BD40-466D-ABC6-DA7CA47DDF54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BCC3370-B7AD-4715-B42A-F82531128245}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>